--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="220">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -310,52 +310,40 @@
     <t>WEIGHTED ENROLLMENT POPULATIONS</t>
   </si>
   <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
     <t>Special Education (SPED)</t>
   </si>
   <si>
-    <t>3  /  4  /  5  /  6  /  6</t>
-  </si>
-  <si>
     <t>English Language Learners (ELL)</t>
   </si>
   <si>
-    <t>2  /  3  /  4  /  5  /  5</t>
-  </si>
-  <si>
     <t>Economically Disadvantaged</t>
   </si>
   <si>
-    <t>5  /  7  /  9  /  10  /  12</t>
-  </si>
-  <si>
     <t>Total Weighted Students</t>
   </si>
   <si>
-    <t>10  /  14  /  18  /  21  /  23</t>
-  </si>
-  <si>
     <t>Weighted % of Enrollment</t>
   </si>
   <si>
-    <t>67%  /  64%  /  60%  /  58%  /  57%</t>
-  </si>
-  <si>
     <t>Revenue &amp; Expense Drivers</t>
-  </si>
-  <si>
-    <t>Year 1</t>
-  </si>
-  <si>
-    <t>Year 2</t>
-  </si>
-  <si>
-    <t>Year 3</t>
-  </si>
-  <si>
-    <t>Year 4</t>
-  </si>
-  <si>
-    <t>Year 5</t>
   </si>
   <si>
     <t>Enrollment</t>
@@ -953,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -987,11 +975,18 @@
     <xf numFmtId="166" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1789,7 +1784,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1810,528 +1805,528 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="48" t="s">
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="32">
+        <v>15</v>
+      </c>
+      <c r="D7" s="32">
+        <v>22</v>
+      </c>
+      <c r="E7" s="32">
+        <v>30</v>
+      </c>
+      <c r="F7" s="32">
+        <v>36</v>
+      </c>
+      <c r="G7" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="C8" s="33">
+        <v>108000</v>
+      </c>
+      <c r="D8" s="33">
+        <v>161620</v>
+      </c>
+      <c r="E8" s="33">
+        <v>225789</v>
+      </c>
+      <c r="F8" s="33">
+        <v>278367.204</v>
+      </c>
+      <c r="G8" s="33">
+        <v>318142.46680000005</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="50" t="s">
+      <c r="C9" s="33">
+        <v>93600</v>
+      </c>
+      <c r="D9" s="33">
+        <v>96408</v>
+      </c>
+      <c r="E9" s="33">
+        <v>99300.23999999999</v>
+      </c>
+      <c r="F9" s="33">
+        <v>141617.4192</v>
+      </c>
+      <c r="G9" s="33">
+        <v>145865.94177600002</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="51" t="s">
+      <c r="C10" s="33">
+        <v>35550</v>
+      </c>
+      <c r="D10" s="33">
+        <v>45522.86666666667</v>
+      </c>
+      <c r="E10" s="33">
+        <v>63304.53602635659</v>
+      </c>
+      <c r="F10" s="33">
+        <v>90773.3936127556</v>
+      </c>
+      <c r="G10" s="33">
+        <v>131957.43501823914</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="31">
-        <v>15</v>
-      </c>
-      <c r="D7" s="31">
-        <v>22</v>
-      </c>
-      <c r="E7" s="31">
-        <v>30</v>
-      </c>
-      <c r="F7" s="31">
-        <v>36</v>
-      </c>
-      <c r="G7" s="31">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="C11" s="33">
+        <v>0</v>
+      </c>
+      <c r="D11" s="33">
+        <v>0</v>
+      </c>
+      <c r="E11" s="33">
+        <v>0</v>
+      </c>
+      <c r="F11" s="33">
+        <v>0</v>
+      </c>
+      <c r="G11" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="36">
+        <v>-21150</v>
+      </c>
+      <c r="D12" s="37">
+        <v>19689.13333333333</v>
+      </c>
+      <c r="E12" s="37">
+        <v>63184.22397364341</v>
+      </c>
+      <c r="F12" s="37">
+        <v>45976.391187244444</v>
+      </c>
+      <c r="G12" s="37">
+        <v>40319.090005760896</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="36">
+        <v>-21150</v>
+      </c>
+      <c r="D13" s="36">
+        <v>-1460.8666666666686</v>
+      </c>
+      <c r="E13" s="37">
+        <v>61723.357306976744</v>
+      </c>
+      <c r="F13" s="37">
+        <v>107699.74849422119</v>
+      </c>
+      <c r="G13" s="37">
+        <v>148018.83849998208</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="53">
+        <v>-0.19583333333333333</v>
+      </c>
+      <c r="D14" s="54">
+        <v>0.12182361918904425</v>
+      </c>
+      <c r="E14" s="54">
+        <v>0.27983747646538765</v>
+      </c>
+      <c r="F14" s="54">
+        <v>0.16516453995508912</v>
+      </c>
+      <c r="G14" s="54">
+        <v>0.12673281379661727</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="32">
-        <v>108000</v>
-      </c>
-      <c r="D8" s="32">
-        <v>161620</v>
-      </c>
-      <c r="E8" s="32">
-        <v>225789</v>
-      </c>
-      <c r="F8" s="32">
-        <v>278367.204</v>
-      </c>
-      <c r="G8" s="32">
-        <v>318142.46680000005</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
+      <c r="C15" s="55">
+        <v>7200</v>
+      </c>
+      <c r="D15" s="55">
+        <v>7346.363636363636</v>
+      </c>
+      <c r="E15" s="55">
+        <v>7526.3</v>
+      </c>
+      <c r="F15" s="55">
+        <v>7732.422333333334</v>
+      </c>
+      <c r="G15" s="55">
+        <v>7953.561670000001</v>
+      </c>
+      <c r="H15" s="56" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="32">
-        <v>93600</v>
-      </c>
-      <c r="D9" s="32">
-        <v>96408</v>
-      </c>
-      <c r="E9" s="32">
-        <v>99300.23999999999</v>
-      </c>
-      <c r="F9" s="32">
-        <v>141617.4192</v>
-      </c>
-      <c r="G9" s="32">
-        <v>145865.94177600002</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="32">
-        <v>35550</v>
-      </c>
-      <c r="D10" s="32">
-        <v>45522.86666666667</v>
-      </c>
-      <c r="E10" s="32">
-        <v>63304.53602635659</v>
-      </c>
-      <c r="F10" s="32">
-        <v>90773.3936127556</v>
-      </c>
-      <c r="G10" s="32">
-        <v>131957.43501823914</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="30" t="s">
+      <c r="C16" s="53">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="D16" s="57">
+        <v>0.5965103328795941</v>
+      </c>
+      <c r="E16" s="54">
+        <v>0.439792195368242</v>
+      </c>
+      <c r="F16" s="54">
+        <v>0.5087431894455497</v>
+      </c>
+      <c r="G16" s="54">
+        <v>0.4584925214265674</v>
+      </c>
+      <c r="H16" s="56" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="32">
-        <v>0</v>
-      </c>
-      <c r="D11" s="32">
-        <v>0</v>
-      </c>
-      <c r="E11" s="32">
-        <v>0</v>
-      </c>
-      <c r="F11" s="32">
-        <v>0</v>
-      </c>
-      <c r="G11" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="35">
-        <v>-21150</v>
-      </c>
-      <c r="D12" s="36">
-        <v>19689.13333333333</v>
-      </c>
-      <c r="E12" s="36">
-        <v>63184.22397364341</v>
-      </c>
-      <c r="F12" s="36">
-        <v>45976.391187244444</v>
-      </c>
-      <c r="G12" s="36">
-        <v>40319.090005760896</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C13" s="35">
-        <v>-21150</v>
-      </c>
-      <c r="D13" s="35">
-        <v>-1460.8666666666686</v>
-      </c>
-      <c r="E13" s="36">
-        <v>61723.357306976744</v>
-      </c>
-      <c r="F13" s="36">
-        <v>107699.74849422119</v>
-      </c>
-      <c r="G13" s="36">
-        <v>148018.83849998208</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="52">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="53">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="D17" s="57">
+        <v>0.16429278554634325</v>
+      </c>
+      <c r="E17" s="54">
+        <v>0.12103325269620419</v>
+      </c>
+      <c r="F17" s="54">
+        <v>0.10103766643260505</v>
+      </c>
+      <c r="G17" s="54">
+        <v>0.09098580037985765</v>
+      </c>
+      <c r="H17" s="56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="53">
         <v>-0.19583333333333333</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D18" s="54">
         <v>0.12182361918904425</v>
       </c>
-      <c r="E14" s="53">
-        <v>0.27983747646538765</v>
-      </c>
-      <c r="F14" s="53">
-        <v>0.16516453995508912</v>
-      </c>
-      <c r="G14" s="53">
+      <c r="E18" s="54">
+        <v>0.2798374764653877</v>
+      </c>
+      <c r="F18" s="54">
+        <v>0.16516453995508906</v>
+      </c>
+      <c r="G18" s="54">
         <v>0.12673281379661727</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="C15" s="54">
-        <v>7200</v>
-      </c>
-      <c r="D15" s="54">
-        <v>7346.363636363636</v>
-      </c>
-      <c r="E15" s="54">
-        <v>7526.3</v>
-      </c>
-      <c r="F15" s="54">
-        <v>7732.422333333334</v>
-      </c>
-      <c r="G15" s="54">
-        <v>7953.561670000001</v>
-      </c>
-      <c r="H15" s="55" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
+      <c r="H18" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="52">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="D16" s="56">
-        <v>0.5965103328795941</v>
-      </c>
-      <c r="E16" s="53">
-        <v>0.439792195368242</v>
-      </c>
-      <c r="F16" s="53">
-        <v>0.5087431894455497</v>
-      </c>
-      <c r="G16" s="53">
-        <v>0.4584925214265674</v>
-      </c>
-      <c r="H16" s="55" t="s">
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="34" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="33" t="s">
+      <c r="C19" s="58">
+        <v>2</v>
+      </c>
+      <c r="D19" s="58">
+        <v>2</v>
+      </c>
+      <c r="E19" s="58">
+        <v>2</v>
+      </c>
+      <c r="F19" s="58">
+        <v>2</v>
+      </c>
+      <c r="G19" s="58">
+        <v>2</v>
+      </c>
+      <c r="H19" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="C17" s="52">
-        <v>0.2388888888888889</v>
-      </c>
-      <c r="D17" s="56">
-        <v>0.16429278554634325</v>
-      </c>
-      <c r="E17" s="53">
-        <v>0.12103325269620419</v>
-      </c>
-      <c r="F17" s="53">
-        <v>0.10103766643260505</v>
-      </c>
-      <c r="G17" s="53">
-        <v>0.09098580037985765</v>
-      </c>
-      <c r="H17" s="55" t="s">
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="34" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="52">
-        <v>-0.19583333333333333</v>
-      </c>
-      <c r="D18" s="53">
-        <v>0.12182361918904425</v>
-      </c>
-      <c r="E18" s="53">
-        <v>0.2798374764653877</v>
-      </c>
-      <c r="F18" s="53">
-        <v>0.16516453995508906</v>
-      </c>
-      <c r="G18" s="53">
-        <v>0.12673281379661727</v>
-      </c>
-      <c r="H18" s="55" t="s">
+      <c r="C20" s="59" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="33" t="s">
+      <c r="D20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="C19" s="57">
-        <v>2</v>
-      </c>
-      <c r="D19" s="57">
-        <v>2</v>
-      </c>
-      <c r="E19" s="57">
-        <v>2</v>
-      </c>
-      <c r="F19" s="57">
-        <v>2</v>
-      </c>
-      <c r="G19" s="57">
-        <v>2</v>
-      </c>
-      <c r="H19" s="55" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="C20" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="D20" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="E20" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="F20" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="G20" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="H20" s="55" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="C21" s="59" t="str">
+      <c r="C21" s="60" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="59" t="str">
+      <c r="D21" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="40" t="str">
+      <c r="E21" s="41" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="59" t="str">
+      <c r="F21" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="59" t="str">
+      <c r="G21" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="55" t="s">
-        <v>107</v>
+      <c r="H21" s="56" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" s="61">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="61">
+        <v>0</v>
+      </c>
+      <c r="E22" s="61">
+        <v>5</v>
+      </c>
+      <c r="F22" s="61">
+        <v>6</v>
+      </c>
+      <c r="G22" s="61">
+        <v>6</v>
+      </c>
+      <c r="H22" s="56" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="C22" s="60">
-        <v>-2</v>
-      </c>
-      <c r="D22" s="60">
-        <v>0</v>
-      </c>
-      <c r="E22" s="60">
-        <v>5</v>
-      </c>
-      <c r="F22" s="60">
-        <v>6</v>
-      </c>
-      <c r="G22" s="60">
-        <v>6</v>
-      </c>
-      <c r="H22" s="55" t="s">
+      <c r="E24" s="51"/>
+      <c r="F24" s="51" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="s">
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C25" s="63" t="s">
         <v>198</v>
       </c>
-      <c r="D24" s="50" t="s">
+      <c r="D25" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50" t="s">
+      <c r="E25" s="64"/>
+      <c r="F25" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C26" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D25" s="63" t="s">
+      <c r="D26" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="E25" s="63"/>
-      <c r="F25" s="64" t="s">
+      <c r="E26" s="64"/>
+      <c r="F26" s="65" t="s">
         <v>204</v>
       </c>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C27" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="D27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E26" s="63"/>
-      <c r="F26" s="64" t="s">
+      <c r="E27" s="64"/>
+      <c r="F27" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="61" t="s">
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C28" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="D28" s="64" t="s">
         <v>210</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="E28" s="64"/>
+      <c r="F28" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="64" t="s">
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="61" t="s">
+      <c r="C29" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="D29" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="C28" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="D28" s="63" t="s">
+      <c r="E29" s="64"/>
+      <c r="F29" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64" t="s">
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="61" t="s">
+      <c r="C30" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="64" t="s">
         <v>216</v>
       </c>
-      <c r="C29" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="D29" s="63" t="s">
+      <c r="E30" s="64"/>
+      <c r="F30" s="65" t="s">
         <v>217</v>
       </c>
-      <c r="E29" s="63"/>
-      <c r="F29" s="64" t="s">
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="67" t="s">
         <v>219</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="D30" s="63" t="s">
-        <v>220</v>
-      </c>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64" t="s">
-        <v>221</v>
-      </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="66" t="s">
-        <v>223</v>
-      </c>
-      <c r="C34" s="66"/>
-      <c r="D34" s="66"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2557,13 +2552,14 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:E72"/>
+  <dimension ref="B1:H72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2965,51 +2961,145 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="66" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B66" s="17" t="s">
         <v>95</v>
       </c>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
-    </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+    </row>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C67" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F67" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G67" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H67" s="24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C68" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="D68" s="20">
+        <v>3</v>
+      </c>
+      <c r="E68" s="20">
+        <v>4</v>
+      </c>
+      <c r="F68" s="20">
+        <v>5</v>
+      </c>
+      <c r="G68" s="20">
+        <v>6</v>
+      </c>
+      <c r="H68" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C69" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="D69" s="20">
+        <v>2</v>
+      </c>
+      <c r="E69" s="20">
+        <v>3</v>
+      </c>
+      <c r="F69" s="20">
+        <v>4</v>
+      </c>
+      <c r="G69" s="20">
+        <v>5</v>
+      </c>
+      <c r="H69" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C70" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D71" s="25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C72" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="D72" s="27" t="s">
+      <c r="D70" s="20">
+        <v>5</v>
+      </c>
+      <c r="E70" s="20">
+        <v>7</v>
+      </c>
+      <c r="F70" s="20">
+        <v>9</v>
+      </c>
+      <c r="G70" s="20">
+        <v>10</v>
+      </c>
+      <c r="H70" s="20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C71" s="25" t="s">
         <v>105</v>
+      </c>
+      <c r="D71" s="26">
+        <f>D68+D69+D70</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="26">
+        <f>E68+E69+E70</f>
+        <v>14</v>
+      </c>
+      <c r="F71" s="26">
+        <f>F68+F69+F70</f>
+        <v>18</v>
+      </c>
+      <c r="G71" s="26">
+        <f>G68+G69+G70</f>
+        <v>21</v>
+      </c>
+      <c r="H71" s="26">
+        <f>H68+H69+H70</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C72" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="28">
+        <f>IF(D12=0,0,D71/D12)</f>
+        <v>0.66666667</v>
+      </c>
+      <c r="E72" s="28">
+        <f>IF(D13=0,0,E71/D13)</f>
+        <v>0.63636364</v>
+      </c>
+      <c r="F72" s="28">
+        <f>IF(D14=0,0,F71/D14)</f>
+        <v>0.6</v>
+      </c>
+      <c r="G72" s="28">
+        <f>IF(D15=0,0,G71/D15)</f>
+        <v>0.58333333</v>
+      </c>
+      <c r="H72" s="28">
+        <f>IF(D16=0,0,H71/D16)</f>
+        <v>0.575</v>
       </c>
     </row>
   </sheetData>
@@ -3021,7 +3111,7 @@
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B66:H66"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -3047,7 +3137,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3056,444 +3146,444 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="28"/>
-      <c r="C3" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="29" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <f>Assumptions!D12</f>
         <v>15</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="32">
         <f>Assumptions!D13</f>
         <v>22</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <f>Assumptions!D14</f>
         <v>30</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="32">
         <f>Assumptions!D15</f>
         <v>36</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="32">
         <f>Assumptions!D16</f>
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="32" t="str">
+      <c r="B5" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="33" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="32" t="str">
+      <c r="D5" s="33" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="32" t="str">
+      <c r="E5" s="33" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="32" t="str">
+      <c r="F5" s="33" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="32" t="str">
+      <c r="G5" s="33" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="32" t="str">
+      <c r="B6" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="33" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="32" t="str">
+      <c r="D6" s="33" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="32" t="str">
+      <c r="E6" s="33" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="32" t="str">
+      <c r="F6" s="33" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="32" t="str">
+      <c r="G6" s="33" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="32">
+      <c r="B7" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="33">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>105000</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="33">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>158620</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="33">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>222789</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="33">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>275367.204</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="33">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>315142.4668</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="32" t="str">
+      <c r="B8" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="33" t="str">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>0</v>
       </c>
-      <c r="D8" s="32" t="str">
+      <c r="D8" s="33" t="str">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>0</v>
       </c>
-      <c r="E8" s="32" t="str">
+      <c r="E8" s="33" t="str">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>0</v>
       </c>
-      <c r="F8" s="32" t="str">
+      <c r="F8" s="33" t="str">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>0</v>
       </c>
-      <c r="G8" s="32" t="str">
+      <c r="G8" s="33" t="str">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="32">
+      <c r="B9" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="33">
         <f>Assumptions!D27</f>
         <v>3000</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>3000</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>3000</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>3000</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>3000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="34">
+      <c r="B10" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>108000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="35">
         <f>D6+D7+D8+D9</f>
         <v>161620</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="35">
         <f>E6+E7+E8+E9</f>
         <v>225789</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <f>F6+F7+F8+F9</f>
         <v>278367.204</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="35">
         <f>G6+G7+G8+G9</f>
         <v>318142.4668</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="31">
+      <c r="B12" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="32">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>1</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>1</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>2</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="32">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="B13" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="33">
         <f>C12*Assumptions!D33</f>
         <v>30000</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>30900</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>31827</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>65563.62</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>67530.5286</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="32">
+      <c r="B14" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="33">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>48000</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>49440</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>50923.2</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>52450.896</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>54024.42288</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="32">
+      <c r="B15" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="33">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>15600</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="33">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>16068</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="33">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>16550.04</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="33">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>23602.9032</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="33">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>24310.990296</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="34">
+      <c r="B16" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="35">
         <f>C13+C14+C15</f>
         <v>93600</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="35">
         <f>D13+D14+D15</f>
         <v>96408</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="35">
         <f>E13+E14+E15</f>
         <v>99300.24</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="35">
         <f>F13+F14+F15</f>
         <v>141617.4192</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="35">
         <f>G13+G14+G15</f>
         <v>145865.941776</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="32">
+      <c r="B18" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="33">
         <f>Assumptions!D46</f>
         <v>21600</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>22230.41860465</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>22879.23663602</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>23546.99110063</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="33">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>24234.2346781</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="32">
+      <c r="B19" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="33">
         <f>Assumptions!D48</f>
         <v>4200</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="33">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>4322.58139535</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="33">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>4448.740457</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="33">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>4578.5816029</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="33">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>4712.21229852</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="32">
+      <c r="B20" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="33">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>6000</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="33">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>13293.86666667</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="33">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>27385.36533333</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="33">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>49644.19027627</v>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="33">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>83328.69271557</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" s="32">
+      <c r="B21" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="33">
         <f>Assumptions!D52</f>
         <v>3750</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>5676</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>8591.1936</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>13003.63063296</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>19682.29532605</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="34">
+      <c r="B22" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="35">
         <f>C18+C19+C20+C21</f>
         <v>35550</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="35">
         <f>D18+D19+D20+D21</f>
         <v>45522.86666667</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="35">
         <f>E18+E19+E20+E21</f>
         <v>63304.53602636</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="35">
         <f>F18+F19+F20+F21</f>
         <v>90773.39361276</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="35">
         <f>G18+G19+G20+G21</f>
         <v>131957.43501824</v>
       </c>
@@ -3526,7 +3616,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3535,415 +3625,415 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="28"/>
-      <c r="C3" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="29" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <f>Drivers!C4</f>
         <v>15</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="32">
         <f>Drivers!D4</f>
         <v>22</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>Drivers!E4</f>
         <v>30</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>Drivers!F4</f>
         <v>36</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>Drivers!G4</f>
         <v>40</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="32" t="str">
+      <c r="B6" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="33" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="32" t="str">
+      <c r="D6" s="33" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="32" t="str">
+      <c r="E6" s="33" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="32" t="str">
+      <c r="F6" s="33" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="32" t="str">
+      <c r="G6" s="33" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="32">
+      <c r="B7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="33">
         <f>Drivers!C7</f>
         <v>105000</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="33">
         <f>Drivers!D7</f>
         <v>158620</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="33">
         <f>Drivers!E7</f>
         <v>222789</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="33">
         <f>Drivers!F7</f>
         <v>275367.204</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="33">
         <f>Drivers!G7</f>
         <v>315142.4668</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="32" t="str">
+      <c r="B8" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="33" t="str">
         <f>Drivers!C8</f>
         <v>0</v>
       </c>
-      <c r="D8" s="32" t="str">
+      <c r="D8" s="33" t="str">
         <f>Drivers!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="32" t="str">
+      <c r="E8" s="33" t="str">
         <f>Drivers!E8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="32" t="str">
+      <c r="F8" s="33" t="str">
         <f>Drivers!F8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="32" t="str">
+      <c r="G8" s="33" t="str">
         <f>Drivers!G8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="32">
+      <c r="B9" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="33">
         <f>Drivers!C9</f>
         <v>3000</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>Drivers!D9</f>
         <v>3000</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>Drivers!E9</f>
         <v>3000</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>Drivers!F9</f>
         <v>3000</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <f>Drivers!G9</f>
         <v>3000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="34">
+      <c r="B10" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="35">
         <f>Drivers!C10</f>
         <v>108000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="35">
         <f>Drivers!D10</f>
         <v>161620</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="35">
         <f>Drivers!E10</f>
         <v>225789</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <f>Drivers!F10</f>
         <v>278367.204</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="35">
         <f>Drivers!G10</f>
         <v>318142.4668</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="32">
+      <c r="B12" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="33">
         <f>Drivers!C16</f>
         <v>93600</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>Drivers!D16</f>
         <v>96408</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>Drivers!E16</f>
         <v>99300.24</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>Drivers!F16</f>
         <v>141617.4192</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="33">
         <f>Drivers!G16</f>
         <v>145865.941776</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="B13" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="33">
         <f>Drivers!C22</f>
         <v>35550</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>Drivers!D22</f>
         <v>45522.86666667</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>Drivers!E22</f>
         <v>63304.53602636</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>Drivers!F22</f>
         <v>90773.39361276</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <f>Drivers!G22</f>
         <v>131957.43501824</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="34">
+      <c r="B15" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="35">
         <f>C12+C13</f>
         <v>129150</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>D12+D13</f>
         <v>141930.86666667</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>E12+E13</f>
         <v>162604.77602636</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>F12+F13</f>
         <v>232390.81281276</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="35">
         <f>G12+G13</f>
         <v>277823.37679424</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="35">
+      <c r="B16" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="36">
         <f>C10-C15</f>
         <v>-21150</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="37">
         <f>D10-D15</f>
         <v>19689.13333333</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="37">
         <f>E10-E15</f>
         <v>63184.22397364</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="37">
         <f>F10-F15</f>
         <v>45976.39118724</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="37">
         <f>G10-G15</f>
         <v>40319.09000576</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="37">
+      <c r="B17" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="38">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.19583333</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="38">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>0.12182362</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="38">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>0.27983748</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="38">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>0.16516454</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="38">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>0.12673281</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="32" t="str">
+      <c r="B19" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="33" t="str">
         <f>'Cash Flow &amp; DSCR'!C9</f>
         <v>0</v>
       </c>
-      <c r="D19" s="32" t="str">
+      <c r="D19" s="33" t="str">
         <f>'Cash Flow &amp; DSCR'!D9</f>
         <v>0</v>
       </c>
-      <c r="E19" s="32" t="str">
+      <c r="E19" s="33" t="str">
         <f>'Cash Flow &amp; DSCR'!E9</f>
         <v>0</v>
       </c>
-      <c r="F19" s="32" t="str">
+      <c r="F19" s="33" t="str">
         <f>'Cash Flow &amp; DSCR'!F9</f>
         <v>0</v>
       </c>
-      <c r="G19" s="32" t="str">
+      <c r="G19" s="33" t="str">
         <f>'Cash Flow &amp; DSCR'!G9</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" s="35">
+      <c r="B21" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="36">
         <f>C16-C19</f>
         <v>-21150</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="37">
         <f>D16-D19</f>
         <v>19689.13333333</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="37">
         <f>E16-E19</f>
         <v>63184.22397364</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="37">
         <f>F16-F19</f>
         <v>45976.39118724</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="37">
         <f>G16-G19</f>
         <v>40319.09000576</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="C22" s="37">
+      <c r="B22" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="38">
         <f>IF(C10&gt;0,C21/C10,0)</f>
         <v>-0.19583333</v>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="38">
         <f>IF(D10&gt;0,D21/D10,0)</f>
         <v>0.12182362</v>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="38">
         <f>IF(E10&gt;0,E21/E10,0)</f>
         <v>0.27983748</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="38">
         <f>IF(F10&gt;0,F21/F10,0)</f>
         <v>0.16516454</v>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="38">
         <f>IF(G10&gt;0,G21/G10,0)</f>
         <v>0.12673281</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C24" s="38">
+      <c r="B24" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="39">
         <f>C21</f>
         <v>-21150</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="39">
         <f>C24+D21</f>
         <v>-1460.86666667</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="39">
         <f>D24+E21</f>
         <v>61723.35730698</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="39">
         <f>E24+F21</f>
         <v>107699.74849422</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24" s="39">
         <f>F24+G21</f>
         <v>148018.83849998</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="C25" s="39" t="s">
+      <c r="B25" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="F25" s="39" t="s">
+      <c r="E25" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="39" t="s">
+      <c r="G25" s="40" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3975,7 +4065,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3984,244 +4074,244 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="28"/>
-      <c r="C3" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>111</v>
+      <c r="B3" s="29"/>
+      <c r="C3" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="38" t="str">
+      <c r="B4" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="39" t="str">
         <f>Assumptions!D57</f>
         <v>0</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="39">
         <f>C16</f>
         <v>-21150</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="39">
         <f>D16</f>
         <v>-1460.86666667</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="39">
         <f>E16</f>
         <v>61723.35730698</v>
       </c>
-      <c r="G4" s="38">
+      <c r="G4" s="39">
         <f>F16</f>
         <v>107699.74849422</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="32">
+      <c r="B5" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="33">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-21150</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="33">
         <f>'5-Year P&amp;L'!D16</f>
         <v>19689.13333333</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="33">
         <f>'5-Year P&amp;L'!E16</f>
         <v>63184.22397364</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="33">
         <f>'5-Year P&amp;L'!F16</f>
         <v>45976.39118724</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="33">
         <f>'5-Year P&amp;L'!G16</f>
         <v>40319.09000576</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="32" t="str">
+      <c r="B7" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="33" t="str">
         <f>Assumptions!D58</f>
         <v>0</v>
       </c>
-      <c r="D7" s="32" t="str">
+      <c r="D7" s="33" t="str">
         <f>Assumptions!D58</f>
         <v>0</v>
       </c>
-      <c r="E7" s="32" t="str">
+      <c r="E7" s="33" t="str">
         <f>Assumptions!D58</f>
         <v>0</v>
       </c>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>Assumptions!D58</f>
         <v>0</v>
       </c>
-      <c r="G7" s="32" t="str">
+      <c r="G7" s="33" t="str">
         <f>Assumptions!D58</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="32" t="str">
+      <c r="B8" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="33" t="str">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="32" t="str">
+      <c r="D8" s="33" t="str">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="32" t="str">
+      <c r="E8" s="33" t="str">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="32" t="str">
+      <c r="F8" s="33" t="str">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="32" t="str">
+      <c r="G8" s="33" t="str">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="34" t="str">
+      <c r="B9" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="35" t="str">
         <f>C7+C8</f>
         <v>0</v>
       </c>
-      <c r="D9" s="34" t="str">
+      <c r="D9" s="35" t="str">
         <f>D7+D8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="34" t="str">
+      <c r="E9" s="35" t="str">
         <f>E7+E8</f>
         <v>0</v>
       </c>
-      <c r="F9" s="34" t="str">
+      <c r="F9" s="35" t="str">
         <f>F7+F8</f>
         <v>0</v>
       </c>
-      <c r="G9" s="34" t="str">
+      <c r="G9" s="35" t="str">
         <f>G7+G8</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C11" s="41" t="str">
+      <c r="B11" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="42" t="str">
         <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
         <v>0</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="43">
         <f>IF(D9&gt;0,D5/D9,IF(D5&gt;0,99.9,0))</f>
         <v>99.9</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="43">
         <f>IF(E9&gt;0,E5/E9,IF(E5&gt;0,99.9,0))</f>
         <v>99.9</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="43">
         <f>IF(F9&gt;0,F5/F9,IF(F5&gt;0,99.9,0))</f>
         <v>99.9</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="43">
         <f>IF(G9&gt;0,G5/G9,IF(G5&gt;0,99.9,0))</f>
         <v>99.9</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="B13" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="33">
         <f>C5-C9</f>
         <v>-21150</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>D5-D9</f>
         <v>19689.13333333</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>E5-E9</f>
         <v>63184.22397364</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>F5-F9</f>
         <v>45976.39118724</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <f>G5-G9</f>
         <v>40319.09000576</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="38">
+      <c r="B14" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="39">
         <f>C5-C9</f>
         <v>-21150</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="39">
         <f>D5-D9</f>
         <v>19689.13333333</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="39">
         <f>E5-E9</f>
         <v>63184.22397364</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="39">
         <f>F5-F9</f>
         <v>45976.39118724</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="39">
         <f>G5-G9</f>
         <v>40319.09000576</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="35">
+      <c r="B16" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="36">
         <f>C4+C14</f>
         <v>-21150</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="36">
         <f>D4+D14</f>
         <v>-1460.86666667</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="37">
         <f>E4+E14</f>
         <v>61723.35730698</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="37">
         <f>F4+F14</f>
         <v>107699.74849422</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="37">
         <f>G4+G14</f>
         <v>148018.83849998</v>
       </c>
@@ -4254,7 +4344,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4263,94 +4353,94 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="28"/>
-      <c r="C3" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>111</v>
+      <c r="B3" s="29"/>
+      <c r="C3" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="C4" s="31">
+      <c r="B4" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="32">
         <f>Drivers!C12</f>
         <v>1</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="32">
         <f>Drivers!D12</f>
         <v>1</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <f>Drivers!E12</f>
         <v>1</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="32">
         <f>Drivers!F12</f>
         <v>2</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="32">
         <f>Drivers!G12</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="31">
+      <c r="B5" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="32">
         <f>Assumptions!D35</f>
         <v>1</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="32">
         <f>Assumptions!D36</f>
         <v>1</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>Assumptions!D37</f>
         <v>1</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>Assumptions!D38</f>
         <v>1</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>Assumptions!D39</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="43">
+      <c r="B6" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="44">
         <f>C4+C5</f>
         <v>2</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="44">
         <f>D4+D5</f>
         <v>2</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="44">
         <f>E4+E5</f>
         <v>2</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="44">
         <f>F4+F5</f>
         <v>3</v>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="44">
         <f>G4+G5</f>
         <v>3</v>
       </c>
@@ -4383,51 +4473,51 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="32" t="str">
+      <c r="B3" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="33" t="str">
         <f>Assumptions!D59</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="37">
+      <c r="B4" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="38">
         <f>Assumptions!D60</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <f>Assumptions!D61</f>
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="38" t="str">
+      <c r="B6" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="39" t="str">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="41" t="str">
+      <c r="B8" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="42" t="str">
         <f>'Cash Flow &amp; DSCR'!C11</f>
         <v>0</v>
       </c>
@@ -4460,136 +4550,136 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="30" t="str">
+      <c r="C3" s="31" t="str">
         <f>Assumptions!D5</f>
         <v>Liberty Learning Co-Op</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="30" t="str">
+      <c r="C4" s="31" t="str">
         <f>Assumptions!D7</f>
         <v>Homeschool Co-Op</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="30" t="str">
+      <c r="C5" s="31" t="str">
         <f>Assumptions!D6</f>
         <v>AZ</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="B6" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="31">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>Assumptions!D16</f>
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="32">
+      <c r="B9" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="33">
         <f>Drivers!G10</f>
         <v>318142.4668</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" s="44">
+      <c r="B10" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="45">
         <f>'5-Year P&amp;L'!G16</f>
         <v>40319.09000576</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" s="28"/>
+      <c r="B12" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="29"/>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="46">
+      <c r="B13" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="47">
         <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
         <v>0.12673281</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="C14" s="37">
+      <c r="B14" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="38">
         <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
         <v>0.45849252</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="C15" s="32">
+      <c r="B15" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="33">
         <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
         <v>7954</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="32">
+      <c r="B16" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="33">
         <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
         <v>6946</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" s="41" t="str">
+      <c r="B17" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="42" t="str">
         <f>'Cash Flow &amp; DSCR'!C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="42">
+      <c r="B18" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" s="43">
         <f>'Cash Flow &amp; DSCR'!G11</f>
         <v>99.9</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C20" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -2552,7 +2552,7 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H72"/>
+  <dimension ref="B1:H69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2961,144 +2961,144 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B66" s="17" t="s">
+    <row r="63" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+    </row>
+    <row r="64" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C64" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E64" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F64" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H64" s="24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C65" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="20">
+        <v>3</v>
+      </c>
+      <c r="E65" s="20">
+        <v>4</v>
+      </c>
+      <c r="F65" s="20">
+        <v>5</v>
+      </c>
+      <c r="G65" s="20">
+        <v>6</v>
+      </c>
+      <c r="H65" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C66" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D66" s="20">
+        <v>2</v>
+      </c>
+      <c r="E66" s="20">
+        <v>3</v>
+      </c>
+      <c r="F66" s="20">
+        <v>4</v>
+      </c>
+      <c r="G66" s="20">
+        <v>5</v>
+      </c>
+      <c r="H66" s="20">
+        <v>5</v>
+      </c>
     </row>
     <row r="67" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C67" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="F67" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="G67" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="H67" s="24" t="s">
-        <v>101</v>
+      <c r="C67" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67" s="20">
+        <v>5</v>
+      </c>
+      <c r="E67" s="20">
+        <v>7</v>
+      </c>
+      <c r="F67" s="20">
+        <v>9</v>
+      </c>
+      <c r="G67" s="20">
+        <v>10</v>
+      </c>
+      <c r="H67" s="20">
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C68" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D68" s="20">
-        <v>3</v>
-      </c>
-      <c r="E68" s="20">
-        <v>4</v>
-      </c>
-      <c r="F68" s="20">
-        <v>5</v>
-      </c>
-      <c r="G68" s="20">
-        <v>6</v>
-      </c>
-      <c r="H68" s="20">
-        <v>6</v>
+      <c r="C68" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D68" s="26">
+        <f>D65+D66+D67</f>
+        <v>10</v>
+      </c>
+      <c r="E68" s="26">
+        <f>E65+E66+E67</f>
+        <v>14</v>
+      </c>
+      <c r="F68" s="26">
+        <f>F65+F66+F67</f>
+        <v>18</v>
+      </c>
+      <c r="G68" s="26">
+        <f>G65+G66+G67</f>
+        <v>21</v>
+      </c>
+      <c r="H68" s="26">
+        <f>H65+H66+H67</f>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C69" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D69" s="20">
-        <v>2</v>
-      </c>
-      <c r="E69" s="20">
-        <v>3</v>
-      </c>
-      <c r="F69" s="20">
-        <v>4</v>
-      </c>
-      <c r="G69" s="20">
-        <v>5</v>
-      </c>
-      <c r="H69" s="20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C70" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D70" s="20">
-        <v>5</v>
-      </c>
-      <c r="E70" s="20">
-        <v>7</v>
-      </c>
-      <c r="F70" s="20">
-        <v>9</v>
-      </c>
-      <c r="G70" s="20">
-        <v>10</v>
-      </c>
-      <c r="H70" s="20">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C71" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" s="26">
-        <f>D68+D69+D70</f>
-        <v>10</v>
-      </c>
-      <c r="E71" s="26">
-        <f>E68+E69+E70</f>
-        <v>14</v>
-      </c>
-      <c r="F71" s="26">
-        <f>F68+F69+F70</f>
-        <v>18</v>
-      </c>
-      <c r="G71" s="26">
-        <f>G68+G69+G70</f>
-        <v>21</v>
-      </c>
-      <c r="H71" s="26">
-        <f>H68+H69+H70</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C72" s="27" t="s">
+      <c r="C69" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="D72" s="28">
-        <f>IF(D12=0,0,D71/D12)</f>
+      <c r="D69" s="28">
+        <f>IF(D12=0,0,D68/D12)</f>
         <v>0.66666667</v>
       </c>
-      <c r="E72" s="28">
-        <f>IF(D13=0,0,E71/D13)</f>
+      <c r="E69" s="28">
+        <f>IF(D13=0,0,E68/D13)</f>
         <v>0.63636364</v>
       </c>
-      <c r="F72" s="28">
-        <f>IF(D14=0,0,F71/D14)</f>
+      <c r="F69" s="28">
+        <f>IF(D14=0,0,F68/D14)</f>
         <v>0.6</v>
       </c>
-      <c r="G72" s="28">
-        <f>IF(D15=0,0,G71/D15)</f>
+      <c r="G69" s="28">
+        <f>IF(D15=0,0,G68/D15)</f>
         <v>0.58333333</v>
       </c>
-      <c r="H72" s="28">
-        <f>IF(D16=0,0,H71/D16)</f>
+      <c r="H69" s="28">
+        <f>IF(D16=0,0,H68/D16)</f>
         <v>0.575</v>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B63:H63"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="223">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -526,6 +526,9 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
+    <t>Days Cash on Hand (Year 1)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -599,6 +602,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -941,7 +950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1036,6 +1045,9 @@
     <xf numFmtId="166" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1066,6 +1078,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1772,7 +1787,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1784,7 +1799,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1805,37 +1820,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="48" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="49" t="s">
+      <c r="B4" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="D4" s="50" t="s">
         <v>172</v>
       </c>
+      <c r="F4" s="51" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="52" t="s">
+      <c r="B6" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="H6" s="52" t="s">
-        <v>174</v>
+      <c r="H6" s="53" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1860,7 +1875,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="33">
         <v>108000</v>
@@ -1880,7 +1895,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C9" s="33">
         <v>93600</v>
@@ -1900,7 +1915,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C10" s="33">
         <v>35550</v>
@@ -1920,7 +1935,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C11" s="33">
         <v>0</v>
@@ -1982,169 +1997,169 @@
       <c r="B14" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="54">
         <v>-0.19583333333333333</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="55">
         <v>0.12182361918904425</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="55">
         <v>0.27983747646538765</v>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="55">
         <v>0.16516453995508912</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="55">
         <v>0.12673281379661727</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="55">
+        <v>180</v>
+      </c>
+      <c r="C15" s="56">
         <v>7200</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="56">
         <v>7346.363636363636</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="56">
         <v>7526.3</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="56">
         <v>7732.422333333334</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="56">
         <v>7953.561670000001</v>
       </c>
-      <c r="H15" s="56" t="s">
-        <v>180</v>
+      <c r="H15" s="57" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="C16" s="53">
+        <v>182</v>
+      </c>
+      <c r="C16" s="54">
         <v>0.8666666666666667</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="58">
         <v>0.5965103328795941</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="55">
         <v>0.439792195368242</v>
       </c>
-      <c r="F16" s="54">
+      <c r="F16" s="55">
         <v>0.5087431894455497</v>
       </c>
-      <c r="G16" s="54">
+      <c r="G16" s="55">
         <v>0.4584925214265674</v>
       </c>
-      <c r="H16" s="56" t="s">
-        <v>182</v>
+      <c r="H16" s="57" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="C17" s="53">
+        <v>184</v>
+      </c>
+      <c r="C17" s="54">
         <v>0.2388888888888889</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="58">
         <v>0.16429278554634325</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="55">
         <v>0.12103325269620419</v>
       </c>
-      <c r="F17" s="54">
+      <c r="F17" s="55">
         <v>0.10103766643260505</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="55">
         <v>0.09098580037985765</v>
       </c>
-      <c r="H17" s="56" t="s">
-        <v>184</v>
+      <c r="H17" s="57" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="54">
         <v>-0.19583333333333333</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="55">
         <v>0.12182361918904425</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="55">
         <v>0.2798374764653877</v>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="55">
         <v>0.16516453995508906</v>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="55">
         <v>0.12673281379661727</v>
       </c>
-      <c r="H18" s="56" t="s">
-        <v>185</v>
+      <c r="H18" s="57" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="C19" s="58">
+        <v>187</v>
+      </c>
+      <c r="C19" s="59">
         <v>2</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="59">
         <v>2</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="59">
         <v>2</v>
       </c>
-      <c r="F19" s="58">
+      <c r="F19" s="59">
         <v>2</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="59">
         <v>2</v>
       </c>
-      <c r="H19" s="56" t="s">
-        <v>187</v>
+      <c r="H19" s="57" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="C20" s="59" t="s">
         <v>189</v>
       </c>
-      <c r="D20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="E20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="G20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="H20" s="56" t="s">
-        <v>189</v>
+      <c r="C20" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="F20" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="60" t="str">
+        <v>191</v>
+      </c>
+      <c r="C21" s="61" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="60" t="str">
+      <c r="D21" s="61" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -2152,188 +2167,209 @@
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="60" t="str">
+      <c r="F21" s="61" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="60" t="str">
+      <c r="G21" s="61" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="56" t="s">
+      <c r="H21" s="57" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="C22" s="61">
+        <v>192</v>
+      </c>
+      <c r="C22" s="62">
         <v>-2</v>
       </c>
-      <c r="D22" s="61">
-        <v>0</v>
-      </c>
-      <c r="E22" s="61">
+      <c r="D22" s="62">
+        <v>0</v>
+      </c>
+      <c r="E22" s="62">
         <v>5</v>
       </c>
-      <c r="F22" s="61">
+      <c r="F22" s="62">
         <v>6</v>
       </c>
-      <c r="G22" s="61">
+      <c r="G22" s="62">
         <v>6</v>
       </c>
-      <c r="H22" s="56" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="51" t="s">
+      <c r="H22" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="C24" s="51" t="s">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="D24" s="51" t="s">
+      <c r="C23" s="62">
+        <v>0</v>
+      </c>
+      <c r="D23" s="62">
+        <v>0</v>
+      </c>
+      <c r="E23" s="63">
+        <v>139</v>
+      </c>
+      <c r="F23" s="63">
+        <v>169</v>
+      </c>
+      <c r="G23" s="63">
+        <v>194</v>
+      </c>
+      <c r="H23" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
+      <c r="C25" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="D25" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="E25" s="52"/>
+      <c r="F25" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="E25" s="64"/>
-      <c r="F25" s="65" t="s">
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="64" t="s">
         <v>200</v>
       </c>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="62" t="s">
+      <c r="C26" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="D26" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="E26" s="66"/>
+      <c r="F26" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="E26" s="64"/>
-      <c r="F26" s="65" t="s">
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="62" t="s">
+      <c r="C27" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="D27" s="66" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="E27" s="66"/>
+      <c r="F27" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65" t="s">
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="62" t="s">
+      <c r="C28" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D28" s="64" t="s">
+      <c r="D28" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="E28" s="64"/>
-      <c r="F28" s="65" t="s">
+      <c r="E28" s="66"/>
+      <c r="F28" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="64" t="s">
         <v>212</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="D29" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="64"/>
-      <c r="F29" s="65" t="s">
+      <c r="E29" s="66"/>
+      <c r="F29" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="64" t="s">
         <v>215</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="D30" s="66" t="s">
         <v>216</v>
       </c>
-      <c r="E30" s="64"/>
-      <c r="F30" s="65" t="s">
+      <c r="E30" s="66"/>
+      <c r="F30" s="67" t="s">
         <v>217</v>
       </c>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="62" t="s">
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" s="66" t="s">
+        <v>219</v>
+      </c>
+      <c r="E31" s="66"/>
+      <c r="F31" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="67" t="s">
-        <v>219</v>
-      </c>
-      <c r="C34" s="67"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
+      <c r="C33" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -2346,8 +2382,10 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4540,7 +4578,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C20"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4677,16 +4715,24 @@
         <v>99.9</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C19" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="228">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -566,6 +566,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -950,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1065,6 +1080,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1787,7 +1808,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2036,356 +2057,439 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="C16" s="54">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="D16" s="58">
-        <v>0.5965103328795941</v>
-      </c>
-      <c r="E16" s="55">
-        <v>0.439792195368242</v>
-      </c>
-      <c r="F16" s="55">
-        <v>0.5087431894455497</v>
-      </c>
-      <c r="G16" s="55">
-        <v>0.4584925214265674</v>
-      </c>
-      <c r="H16" s="57" t="s">
+      <c r="C16" s="39">
+        <v>8610</v>
+      </c>
+      <c r="D16" s="39">
+        <v>6451.40303030303</v>
+      </c>
+      <c r="E16" s="39">
+        <v>5420.159200878553</v>
+      </c>
+      <c r="F16" s="39">
+        <v>6455.300355909877</v>
+      </c>
+      <c r="G16" s="39">
+        <v>6945.584419855979</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="31" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="34" t="s">
+      <c r="C17" s="33">
+        <v>400</v>
+      </c>
+      <c r="D17" s="33">
+        <v>604.2666666666668</v>
+      </c>
+      <c r="E17" s="33">
+        <v>912.8455111111114</v>
+      </c>
+      <c r="F17" s="33">
+        <v>1379.0052854518522</v>
+      </c>
+      <c r="G17" s="33">
+        <v>2083.217317889265</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="C17" s="54">
-        <v>0.2388888888888889</v>
-      </c>
-      <c r="D17" s="58">
-        <v>0.16429278554634325</v>
-      </c>
-      <c r="E17" s="55">
-        <v>0.12103325269620419</v>
-      </c>
-      <c r="F17" s="55">
-        <v>0.10103766643260505</v>
-      </c>
-      <c r="G17" s="55">
-        <v>0.09098580037985765</v>
-      </c>
-      <c r="H17" s="57" t="s">
+      <c r="C18" s="58">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="58">
+        <v>1206.9545454545453</v>
+      </c>
+      <c r="E18" s="58">
+        <v>910.9325697674416</v>
+      </c>
+      <c r="F18" s="58">
+        <v>781.265908431359</v>
+      </c>
+      <c r="G18" s="58">
+        <v>723.6611744155073</v>
+      </c>
+      <c r="H18" s="57" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="54">
-        <v>-0.19583333333333333</v>
-      </c>
-      <c r="D18" s="55">
-        <v>0.12182361918904425</v>
-      </c>
-      <c r="E18" s="55">
-        <v>0.2798374764653877</v>
-      </c>
-      <c r="F18" s="55">
-        <v>0.16516453995508906</v>
-      </c>
-      <c r="G18" s="55">
-        <v>0.12673281379661727</v>
-      </c>
-      <c r="H18" s="57" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="34" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="34" t="s">
-        <v>187</v>
-      </c>
       <c r="C19" s="59">
-        <v>2</v>
-      </c>
-      <c r="D19" s="59">
-        <v>2</v>
-      </c>
-      <c r="E19" s="59">
-        <v>2</v>
-      </c>
-      <c r="F19" s="59">
-        <v>2</v>
-      </c>
-      <c r="G19" s="59">
-        <v>2</v>
-      </c>
-      <c r="H19" s="57" t="s">
-        <v>188</v>
+        <v>-1410</v>
+      </c>
+      <c r="D19" s="45">
+        <v>894.960606060606</v>
+      </c>
+      <c r="E19" s="45">
+        <v>2106.140799121447</v>
+      </c>
+      <c r="F19" s="45">
+        <v>1277.1219774234569</v>
+      </c>
+      <c r="G19" s="45">
+        <v>1007.9772501440224</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="60" t="s">
-        <v>190</v>
-      </c>
-      <c r="E20" s="60" t="s">
-        <v>190</v>
-      </c>
-      <c r="F20" s="60" t="s">
-        <v>190</v>
-      </c>
-      <c r="G20" s="60" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+      <c r="C20" s="54">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0.5965103328795941</v>
+      </c>
+      <c r="E20" s="55">
+        <v>0.439792195368242</v>
+      </c>
+      <c r="F20" s="55">
+        <v>0.5087431894455497</v>
+      </c>
+      <c r="G20" s="55">
+        <v>0.4584925214265674</v>
       </c>
       <c r="H20" s="57" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="54">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.16429278554634325</v>
+      </c>
+      <c r="E21" s="55">
+        <v>0.12103325269620419</v>
+      </c>
+      <c r="F21" s="55">
+        <v>0.10103766643260505</v>
+      </c>
+      <c r="G21" s="55">
+        <v>0.09098580037985765</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="54">
+        <v>-0.19583333333333333</v>
+      </c>
+      <c r="D22" s="55">
+        <v>0.12182361918904425</v>
+      </c>
+      <c r="E22" s="55">
+        <v>0.2798374764653877</v>
+      </c>
+      <c r="F22" s="55">
+        <v>0.16516453995508906</v>
+      </c>
+      <c r="G22" s="55">
+        <v>0.12673281379661727</v>
+      </c>
+      <c r="H22" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="C21" s="61" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" s="61">
+        <v>2</v>
+      </c>
+      <c r="D23" s="61">
+        <v>2</v>
+      </c>
+      <c r="E23" s="61">
+        <v>2</v>
+      </c>
+      <c r="F23" s="61">
+        <v>2</v>
+      </c>
+      <c r="G23" s="61">
+        <v>2</v>
+      </c>
+      <c r="H23" s="57" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="G24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="63" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="61" t="str">
+      <c r="D25" s="63" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="41" t="str">
+      <c r="E25" s="41" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="61" t="str">
+      <c r="F25" s="63" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="61" t="str">
+      <c r="G25" s="63" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H25" s="57" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="C22" s="62">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="64">
         <v>-2</v>
       </c>
-      <c r="D22" s="62">
-        <v>0</v>
-      </c>
-      <c r="E22" s="62">
+      <c r="D26" s="64">
+        <v>0</v>
+      </c>
+      <c r="E26" s="64">
         <v>5</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F26" s="64">
         <v>6</v>
       </c>
-      <c r="G22" s="62">
+      <c r="G26" s="64">
         <v>6</v>
       </c>
-      <c r="H22" s="57" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="34" t="s">
+      <c r="H26" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="64">
+        <v>0</v>
+      </c>
+      <c r="D27" s="64">
+        <v>0</v>
+      </c>
+      <c r="E27" s="65">
+        <v>139</v>
+      </c>
+      <c r="F27" s="65">
+        <v>169</v>
+      </c>
+      <c r="G27" s="65">
         <v>194</v>
       </c>
-      <c r="C23" s="62">
-        <v>0</v>
-      </c>
-      <c r="D23" s="62">
-        <v>0</v>
-      </c>
-      <c r="E23" s="63">
-        <v>139</v>
-      </c>
-      <c r="F23" s="63">
-        <v>169</v>
-      </c>
-      <c r="G23" s="63">
-        <v>194</v>
-      </c>
-      <c r="H23" s="57" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="52" t="s">
-        <v>197</v>
-      </c>
-      <c r="D25" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52" t="s">
-        <v>199</v>
-      </c>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="64" t="s">
+      <c r="H27" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="C26" s="65" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="C29" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="E26" s="66"/>
-      <c r="F26" s="67" t="s">
+      <c r="D29" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="64" t="s">
+      <c r="E29" s="52"/>
+      <c r="F29" s="52" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="66" t="s">
         <v>205</v>
       </c>
-      <c r="D27" s="66" t="s">
+      <c r="C30" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="E27" s="66"/>
-      <c r="F27" s="67" t="s">
+      <c r="D30" s="68" t="s">
         <v>207</v>
       </c>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="64" t="s">
+      <c r="E30" s="68"/>
+      <c r="F30" s="69" t="s">
         <v>208</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="D28" s="66" t="s">
+      <c r="C31" s="70" t="s">
         <v>210</v>
       </c>
-      <c r="E28" s="66"/>
-      <c r="F28" s="67" t="s">
+      <c r="D31" s="68" t="s">
         <v>211</v>
       </c>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="64" t="s">
+      <c r="E31" s="68"/>
+      <c r="F31" s="69" t="s">
         <v>212</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="D29" s="66" t="s">
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="66"/>
-      <c r="F29" s="67" t="s">
+      <c r="C32" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="64" t="s">
+      <c r="D32" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="D30" s="66" t="s">
+      <c r="E32" s="68"/>
+      <c r="F32" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="E30" s="66"/>
-      <c r="F30" s="67" t="s">
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="64" t="s">
+      <c r="C33" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D33" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="D31" s="66" t="s">
+      <c r="E33" s="68"/>
+      <c r="F33" s="69" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="66"/>
-      <c r="F31" s="67" t="s">
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="34" t="s">
+      <c r="C34" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D34" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="69" t="s">
+      <c r="E34" s="68"/>
+      <c r="F34" s="69" t="s">
         <v>222</v>
       </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" s="68"/>
+      <c r="F35" s="69" t="s">
+        <v>225</v>
+      </c>
       <c r="G35" s="69"/>
       <c r="H35" s="69"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="66" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="71" t="s">
+        <v>227</v>
+      </c>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2431,37 +2535,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="220">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -526,9 +526,6 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
-    <t>Days Cash on Hand (Year 1)</t>
-  </si>
-  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -568,21 +565,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -617,12 +599,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -965,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1060,9 +1036,6 @@
     <xf numFmtId="166" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1080,12 +1053,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1099,9 +1066,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1808,7 +1772,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1820,7 +1784,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1841,37 +1805,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="F4" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="F4" s="51" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="51" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="52" t="s">
+      <c r="C6" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="52" t="s">
         <v>174</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="H6" s="53" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1896,7 +1860,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C8" s="33">
         <v>108000</v>
@@ -1916,7 +1880,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C9" s="33">
         <v>93600</v>
@@ -1936,7 +1900,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C10" s="33">
         <v>35550</v>
@@ -1956,7 +1920,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" s="33">
         <v>0</v>
@@ -2018,478 +1982,372 @@
       <c r="B14" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="53">
         <v>-0.19583333333333333</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="54">
         <v>0.12182361918904425</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="54">
         <v>0.27983747646538765</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="54">
         <v>0.16516453995508912</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="54">
         <v>0.12673281379661727</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" s="55">
+        <v>7200</v>
+      </c>
+      <c r="D15" s="55">
+        <v>7346.363636363636</v>
+      </c>
+      <c r="E15" s="55">
+        <v>7526.3</v>
+      </c>
+      <c r="F15" s="55">
+        <v>7732.422333333334</v>
+      </c>
+      <c r="G15" s="55">
+        <v>7953.561670000001</v>
+      </c>
+      <c r="H15" s="56" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="56">
-        <v>7200</v>
-      </c>
-      <c r="D15" s="56">
-        <v>7346.363636363636</v>
-      </c>
-      <c r="E15" s="56">
-        <v>7526.3</v>
-      </c>
-      <c r="F15" s="56">
-        <v>7732.422333333334</v>
-      </c>
-      <c r="G15" s="56">
-        <v>7953.561670000001</v>
-      </c>
-      <c r="H15" s="57" t="s">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="34" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="34" t="s">
+      <c r="C16" s="53">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="D16" s="57">
+        <v>0.5965103328795941</v>
+      </c>
+      <c r="E16" s="54">
+        <v>0.439792195368242</v>
+      </c>
+      <c r="F16" s="54">
+        <v>0.5087431894455497</v>
+      </c>
+      <c r="G16" s="54">
+        <v>0.4584925214265674</v>
+      </c>
+      <c r="H16" s="56" t="s">
         <v>182</v>
       </c>
-      <c r="C16" s="39">
-        <v>8610</v>
-      </c>
-      <c r="D16" s="39">
-        <v>6451.40303030303</v>
-      </c>
-      <c r="E16" s="39">
-        <v>5420.159200878553</v>
-      </c>
-      <c r="F16" s="39">
-        <v>6455.300355909877</v>
-      </c>
-      <c r="G16" s="39">
-        <v>6945.584419855979</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="33">
-        <v>400</v>
-      </c>
-      <c r="D17" s="33">
-        <v>604.2666666666668</v>
-      </c>
-      <c r="E17" s="33">
-        <v>912.8455111111114</v>
-      </c>
-      <c r="F17" s="33">
-        <v>1379.0052854518522</v>
-      </c>
-      <c r="G17" s="33">
-        <v>2083.217317889265</v>
+      <c r="C17" s="53">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="D17" s="57">
+        <v>0.16429278554634325</v>
+      </c>
+      <c r="E17" s="54">
+        <v>0.12103325269620419</v>
+      </c>
+      <c r="F17" s="54">
+        <v>0.10103766643260505</v>
+      </c>
+      <c r="G17" s="54">
+        <v>0.09098580037985765</v>
+      </c>
+      <c r="H17" s="56" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="C18" s="58">
-        <v>1720</v>
-      </c>
-      <c r="D18" s="58">
-        <v>1206.9545454545453</v>
-      </c>
-      <c r="E18" s="58">
-        <v>910.9325697674416</v>
-      </c>
-      <c r="F18" s="58">
-        <v>781.265908431359</v>
-      </c>
-      <c r="G18" s="58">
-        <v>723.6611744155073</v>
-      </c>
-      <c r="H18" s="57" t="s">
+      <c r="B18" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="53">
+        <v>-0.19583333333333333</v>
+      </c>
+      <c r="D18" s="54">
+        <v>0.12182361918904425</v>
+      </c>
+      <c r="E18" s="54">
+        <v>0.2798374764653877</v>
+      </c>
+      <c r="F18" s="54">
+        <v>0.16516453995508906</v>
+      </c>
+      <c r="G18" s="54">
+        <v>0.12673281379661727</v>
+      </c>
+      <c r="H18" s="56" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="C19" s="59">
-        <v>-1410</v>
-      </c>
-      <c r="D19" s="45">
-        <v>894.960606060606</v>
-      </c>
-      <c r="E19" s="45">
-        <v>2106.140799121447</v>
-      </c>
-      <c r="F19" s="45">
-        <v>1277.1219774234569</v>
-      </c>
-      <c r="G19" s="45">
-        <v>1007.9772501440224</v>
+      <c r="C19" s="58">
+        <v>2</v>
+      </c>
+      <c r="D19" s="58">
+        <v>2</v>
+      </c>
+      <c r="E19" s="58">
+        <v>2</v>
+      </c>
+      <c r="F19" s="58">
+        <v>2</v>
+      </c>
+      <c r="G19" s="58">
+        <v>2</v>
+      </c>
+      <c r="H19" s="56" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="C20" s="54">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="D20" s="60">
-        <v>0.5965103328795941</v>
-      </c>
-      <c r="E20" s="55">
-        <v>0.439792195368242</v>
-      </c>
-      <c r="F20" s="55">
-        <v>0.5087431894455497</v>
-      </c>
-      <c r="G20" s="55">
-        <v>0.4584925214265674</v>
-      </c>
-      <c r="H20" s="57" t="s">
         <v>188</v>
+      </c>
+      <c r="C20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="56" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="54">
-        <v>0.2388888888888889</v>
-      </c>
-      <c r="D21" s="60">
-        <v>0.16429278554634325</v>
-      </c>
-      <c r="E21" s="55">
-        <v>0.12103325269620419</v>
-      </c>
-      <c r="F21" s="55">
-        <v>0.10103766643260505</v>
-      </c>
-      <c r="G21" s="55">
-        <v>0.09098580037985765</v>
-      </c>
-      <c r="H21" s="57" t="s">
         <v>190</v>
+      </c>
+      <c r="C21" s="60" t="str">
+        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="60" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="41" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="F21" s="60" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="60" t="str">
+        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="56" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" s="54">
-        <v>-0.19583333333333333</v>
-      </c>
-      <c r="D22" s="55">
-        <v>0.12182361918904425</v>
-      </c>
-      <c r="E22" s="55">
-        <v>0.2798374764653877</v>
-      </c>
-      <c r="F22" s="55">
-        <v>0.16516453995508906</v>
-      </c>
-      <c r="G22" s="55">
-        <v>0.12673281379661727</v>
-      </c>
-      <c r="H22" s="57" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="34" t="s">
+      <c r="C22" s="61">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="61">
+        <v>0</v>
+      </c>
+      <c r="E22" s="61">
+        <v>5</v>
+      </c>
+      <c r="F22" s="61">
+        <v>6</v>
+      </c>
+      <c r="G22" s="61">
+        <v>6</v>
+      </c>
+      <c r="H22" s="56" t="s">
         <v>192</v>
       </c>
-      <c r="C23" s="61">
-        <v>2</v>
-      </c>
-      <c r="D23" s="61">
-        <v>2</v>
-      </c>
-      <c r="E23" s="61">
-        <v>2</v>
-      </c>
-      <c r="F23" s="61">
-        <v>2</v>
-      </c>
-      <c r="G23" s="61">
-        <v>2</v>
-      </c>
-      <c r="H23" s="57" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="51" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="34" t="s">
+      <c r="C24" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="D24" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="D24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="E24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="F24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="G24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="H24" s="57" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="34" t="s">
+      <c r="E24" s="51"/>
+      <c r="F24" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="63" t="str">
-        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="63" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="41" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="F25" s="63" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="63" t="str">
-        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="57" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="34" t="s">
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="C26" s="64">
-        <v>-2</v>
-      </c>
-      <c r="D26" s="64">
-        <v>0</v>
-      </c>
-      <c r="E26" s="64">
-        <v>5</v>
-      </c>
-      <c r="F26" s="64">
-        <v>6</v>
-      </c>
-      <c r="G26" s="64">
-        <v>6</v>
-      </c>
-      <c r="H26" s="57" t="s">
+      <c r="C25" s="63" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="34" t="s">
+      <c r="D25" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="C27" s="64">
-        <v>0</v>
-      </c>
-      <c r="D27" s="64">
-        <v>0</v>
-      </c>
-      <c r="E27" s="65">
-        <v>139</v>
-      </c>
-      <c r="F27" s="65">
-        <v>169</v>
-      </c>
-      <c r="G27" s="65">
-        <v>194</v>
-      </c>
-      <c r="H27" s="57" t="s">
+      <c r="E25" s="64"/>
+      <c r="F25" s="65" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="52" t="s">
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C26" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D26" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52" t="s">
+      <c r="E26" s="64"/>
+      <c r="F26" s="65" t="s">
         <v>204</v>
       </c>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="D27" s="64" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="64"/>
+      <c r="F27" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" s="64"/>
+      <c r="F28" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="62" t="s">
+        <v>212</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="D29" s="64" t="s">
+        <v>213</v>
+      </c>
+      <c r="E29" s="64"/>
+      <c r="F29" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="66" t="s">
-        <v>205</v>
-      </c>
-      <c r="C30" s="67" t="s">
+      <c r="B30" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="D30" s="68" t="s">
-        <v>207</v>
-      </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69" t="s">
-        <v>208</v>
-      </c>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="66" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="70" t="s">
-        <v>210</v>
-      </c>
-      <c r="D31" s="68" t="s">
-        <v>211</v>
-      </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69" t="s">
-        <v>212</v>
-      </c>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="66" t="s">
-        <v>213</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="D32" s="68" t="s">
-        <v>215</v>
-      </c>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69" t="s">
+      <c r="D30" s="64" t="s">
         <v>216</v>
       </c>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
+      <c r="E30" s="64"/>
+      <c r="F30" s="65" t="s">
         <v>217</v>
       </c>
-      <c r="C33" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="D33" s="68" t="s">
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="E33" s="68"/>
-      <c r="F33" s="69" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="67" t="s">
         <v>219</v>
       </c>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="66" t="s">
-        <v>220</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="D34" s="68" t="s">
-        <v>221</v>
-      </c>
-      <c r="E34" s="68"/>
-      <c r="F34" s="69" t="s">
-        <v>222</v>
-      </c>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="66" t="s">
-        <v>223</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="D35" s="68" t="s">
-        <v>224</v>
-      </c>
-      <c r="E35" s="68"/>
-      <c r="F35" s="69" t="s">
-        <v>225</v>
-      </c>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="71" t="s">
-        <v>227</v>
-      </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2535,37 +2393,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4682,7 +4540,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C21"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4819,24 +4677,16 @@
         <v>99.9</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="C19" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C21" s="12"/>
+      <c r="C20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="228">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -526,6 +526,9 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
+    <t>Days Cash on Hand (Year 1)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -565,6 +568,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -599,6 +617,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -941,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1036,6 +1060,9 @@
     <xf numFmtId="166" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1053,6 +1080,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1066,6 +1099,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1772,7 +1808,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1784,7 +1820,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1805,37 +1841,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="48" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="49" t="s">
+      <c r="B4" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="D4" s="50" t="s">
         <v>172</v>
       </c>
+      <c r="F4" s="51" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="52" t="s">
+      <c r="B6" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="H6" s="52" t="s">
-        <v>174</v>
+      <c r="H6" s="53" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1860,7 +1896,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="33">
         <v>108000</v>
@@ -1880,7 +1916,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C9" s="33">
         <v>93600</v>
@@ -1900,7 +1936,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C10" s="33">
         <v>35550</v>
@@ -1920,7 +1956,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C11" s="33">
         <v>0</v>
@@ -1982,372 +2018,478 @@
       <c r="B14" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="54">
         <v>-0.19583333333333333</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="55">
         <v>0.12182361918904425</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="55">
         <v>0.27983747646538765</v>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="55">
         <v>0.16516453995508912</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="55">
         <v>0.12673281379661727</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="55">
+        <v>180</v>
+      </c>
+      <c r="C15" s="56">
         <v>7200</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="56">
         <v>7346.363636363636</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="56">
         <v>7526.3</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="56">
         <v>7732.422333333334</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="56">
         <v>7953.561670000001</v>
       </c>
-      <c r="H15" s="56" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H15" s="57" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="C16" s="53">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="D16" s="57">
-        <v>0.5965103328795941</v>
-      </c>
-      <c r="E16" s="54">
-        <v>0.439792195368242</v>
-      </c>
-      <c r="F16" s="54">
-        <v>0.5087431894455497</v>
-      </c>
-      <c r="G16" s="54">
-        <v>0.4584925214265674</v>
-      </c>
-      <c r="H16" s="56" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="34" t="s">
+      <c r="C16" s="39">
+        <v>8610</v>
+      </c>
+      <c r="D16" s="39">
+        <v>6451.40303030303</v>
+      </c>
+      <c r="E16" s="39">
+        <v>5420.159200878553</v>
+      </c>
+      <c r="F16" s="39">
+        <v>6455.300355909877</v>
+      </c>
+      <c r="G16" s="39">
+        <v>6945.584419855979</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="53">
-        <v>0.2388888888888889</v>
-      </c>
-      <c r="D17" s="57">
-        <v>0.16429278554634325</v>
-      </c>
-      <c r="E17" s="54">
-        <v>0.12103325269620419</v>
-      </c>
-      <c r="F17" s="54">
-        <v>0.10103766643260505</v>
-      </c>
-      <c r="G17" s="54">
-        <v>0.09098580037985765</v>
-      </c>
-      <c r="H17" s="56" t="s">
+      <c r="C17" s="33">
+        <v>400</v>
+      </c>
+      <c r="D17" s="33">
+        <v>604.2666666666668</v>
+      </c>
+      <c r="E17" s="33">
+        <v>912.8455111111114</v>
+      </c>
+      <c r="F17" s="33">
+        <v>1379.0052854518522</v>
+      </c>
+      <c r="G17" s="33">
+        <v>2083.217317889265</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="31" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="53">
-        <v>-0.19583333333333333</v>
-      </c>
-      <c r="D18" s="54">
-        <v>0.12182361918904425</v>
-      </c>
-      <c r="E18" s="54">
-        <v>0.2798374764653877</v>
-      </c>
-      <c r="F18" s="54">
-        <v>0.16516453995508906</v>
-      </c>
-      <c r="G18" s="54">
-        <v>0.12673281379661727</v>
-      </c>
-      <c r="H18" s="56" t="s">
+      <c r="C18" s="58">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="58">
+        <v>1206.9545454545453</v>
+      </c>
+      <c r="E18" s="58">
+        <v>910.9325697674416</v>
+      </c>
+      <c r="F18" s="58">
+        <v>781.265908431359</v>
+      </c>
+      <c r="G18" s="58">
+        <v>723.6611744155073</v>
+      </c>
+      <c r="H18" s="57" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="C19" s="58">
-        <v>2</v>
-      </c>
-      <c r="D19" s="58">
-        <v>2</v>
-      </c>
-      <c r="E19" s="58">
-        <v>2</v>
-      </c>
-      <c r="F19" s="58">
-        <v>2</v>
-      </c>
-      <c r="G19" s="58">
-        <v>2</v>
-      </c>
-      <c r="H19" s="56" t="s">
-        <v>187</v>
+      <c r="C19" s="59">
+        <v>-1410</v>
+      </c>
+      <c r="D19" s="45">
+        <v>894.960606060606</v>
+      </c>
+      <c r="E19" s="45">
+        <v>2106.140799121447</v>
+      </c>
+      <c r="F19" s="45">
+        <v>1277.1219774234569</v>
+      </c>
+      <c r="G19" s="45">
+        <v>1007.9772501440224</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="54">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0.5965103328795941</v>
+      </c>
+      <c r="E20" s="55">
+        <v>0.439792195368242</v>
+      </c>
+      <c r="F20" s="55">
+        <v>0.5087431894455497</v>
+      </c>
+      <c r="G20" s="55">
+        <v>0.4584925214265674</v>
+      </c>
+      <c r="H20" s="57" t="s">
         <v>188</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="D20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="E20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="G20" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="H20" s="56" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="54">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.16429278554634325</v>
+      </c>
+      <c r="E21" s="55">
+        <v>0.12103325269620419</v>
+      </c>
+      <c r="F21" s="55">
+        <v>0.10103766643260505</v>
+      </c>
+      <c r="G21" s="55">
+        <v>0.09098580037985765</v>
+      </c>
+      <c r="H21" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="C21" s="60" t="str">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="54">
+        <v>-0.19583333333333333</v>
+      </c>
+      <c r="D22" s="55">
+        <v>0.12182361918904425</v>
+      </c>
+      <c r="E22" s="55">
+        <v>0.2798374764653877</v>
+      </c>
+      <c r="F22" s="55">
+        <v>0.16516453995508906</v>
+      </c>
+      <c r="G22" s="55">
+        <v>0.12673281379661727</v>
+      </c>
+      <c r="H22" s="57" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" s="61">
+        <v>2</v>
+      </c>
+      <c r="D23" s="61">
+        <v>2</v>
+      </c>
+      <c r="E23" s="61">
+        <v>2</v>
+      </c>
+      <c r="F23" s="61">
+        <v>2</v>
+      </c>
+      <c r="G23" s="61">
+        <v>2</v>
+      </c>
+      <c r="H23" s="57" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="G24" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="63" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="60" t="str">
+      <c r="D25" s="63" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="41" t="str">
+      <c r="E25" s="41" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="60" t="str">
+      <c r="F25" s="63" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="60" t="str">
+      <c r="G25" s="63" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="56" t="s">
+      <c r="H25" s="57" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="C22" s="61">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="64">
         <v>-2</v>
       </c>
-      <c r="D22" s="61">
-        <v>0</v>
-      </c>
-      <c r="E22" s="61">
+      <c r="D26" s="64">
+        <v>0</v>
+      </c>
+      <c r="E26" s="64">
         <v>5</v>
       </c>
-      <c r="F22" s="61">
+      <c r="F26" s="64">
         <v>6</v>
       </c>
-      <c r="G22" s="61">
+      <c r="G26" s="64">
         <v>6</v>
       </c>
-      <c r="H22" s="56" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="C24" s="51" t="s">
+      <c r="H26" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="64">
+        <v>0</v>
+      </c>
+      <c r="D27" s="64">
+        <v>0</v>
+      </c>
+      <c r="E27" s="65">
+        <v>139</v>
+      </c>
+      <c r="F27" s="65">
+        <v>169</v>
+      </c>
+      <c r="G27" s="65">
         <v>194</v>
       </c>
-      <c r="D24" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
-        <v>197</v>
-      </c>
-      <c r="C25" s="63" t="s">
-        <v>198</v>
-      </c>
-      <c r="D25" s="64" t="s">
-        <v>199</v>
-      </c>
-      <c r="E25" s="64"/>
-      <c r="F25" s="65" t="s">
+      <c r="H27" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="62" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C29" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="D29" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="E26" s="64"/>
-      <c r="F26" s="65" t="s">
+      <c r="E29" s="52"/>
+      <c r="F29" s="52" t="s">
         <v>204</v>
       </c>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="62" t="s">
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="66" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C30" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D30" s="68" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65" t="s">
+      <c r="E30" s="68"/>
+      <c r="F30" s="69" t="s">
         <v>208</v>
       </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="62" t="s">
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D28" s="64" t="s">
+      <c r="C31" s="70" t="s">
         <v>210</v>
       </c>
-      <c r="E28" s="64"/>
-      <c r="F28" s="65" t="s">
+      <c r="D31" s="68" t="s">
         <v>211</v>
       </c>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="62" t="s">
+      <c r="E31" s="68"/>
+      <c r="F31" s="69" t="s">
         <v>212</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="64" t="s">
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="64"/>
-      <c r="F29" s="65" t="s">
+      <c r="C32" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="62" t="s">
+      <c r="D32" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="64" t="s">
+      <c r="E32" s="68"/>
+      <c r="F32" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="E30" s="64"/>
-      <c r="F30" s="65" t="s">
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="62" t="s">
+      <c r="C33" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D33" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33" s="68"/>
+      <c r="F33" s="69" t="s">
+        <v>219</v>
+      </c>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="66" t="s">
+        <v>220</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D34" s="68" t="s">
+        <v>221</v>
+      </c>
+      <c r="E34" s="68"/>
+      <c r="F34" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" s="68"/>
+      <c r="F35" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="67" t="s">
-        <v>219</v>
-      </c>
-      <c r="C34" s="67"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
+      <c r="C37" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="71" t="s">
+        <v>227</v>
+      </c>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2393,37 +2535,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4540,7 +4682,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C20"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4677,16 +4819,24 @@
         <v>99.9</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C19" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -13,14 +13,15 @@
     <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
+    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="231">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -28,7 +29,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · llc_single</t>
+    <t>Generated April 29, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -142,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -532,6 +533,15 @@
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
+  </si>
+  <si>
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
@@ -655,7 +665,7 @@
     <t>○ Needs attention</t>
   </si>
   <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 1. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -694,7 +704,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>6.4 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>5.8 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -965,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1062,6 +1072,12 @@
     </xf>
     <xf numFmtId="3" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1808,6 +1824,72 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1820,7 +1902,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1841,37 +1923,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>173</v>
+      <c r="B4" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="53" t="s">
+      <c r="B6" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="G6" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="H6" s="53" t="s">
-        <v>175</v>
+      <c r="H6" s="55" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1896,7 +1978,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C8" s="33">
         <v>108000</v>
@@ -1916,7 +1998,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C9" s="33">
         <v>93600</v>
@@ -1936,27 +2018,27 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C10" s="33">
-        <v>35550</v>
+        <v>40050</v>
       </c>
       <c r="D10" s="33">
-        <v>45522.86666666667</v>
+        <v>50022.86666666667</v>
       </c>
       <c r="E10" s="33">
-        <v>63304.53602635659</v>
+        <v>67264.97588090204</v>
       </c>
       <c r="F10" s="33">
-        <v>90773.3936127556</v>
+        <v>93251.63231718403</v>
       </c>
       <c r="G10" s="33">
-        <v>131957.43501823914</v>
+        <v>131371.32179852598</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C11" s="33">
         <v>0</v>
@@ -1979,19 +2061,19 @@
         <v>133</v>
       </c>
       <c r="C12" s="36">
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D12" s="37">
-        <v>19689.13333333333</v>
+        <v>15189.133333333331</v>
       </c>
       <c r="E12" s="37">
-        <v>63184.22397364341</v>
+        <v>59223.78411909798</v>
       </c>
       <c r="F12" s="37">
-        <v>45976.391187244444</v>
+        <v>43498.15248281599</v>
       </c>
       <c r="G12" s="37">
-        <v>40319.090005760896</v>
+        <v>40905.20322547405</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -1999,87 +2081,87 @@
         <v>147</v>
       </c>
       <c r="C13" s="36">
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D13" s="36">
-        <v>-1460.8666666666686</v>
+        <v>-10460.866666666669</v>
       </c>
       <c r="E13" s="37">
-        <v>61723.357306976744</v>
+        <v>48762.91745243131</v>
       </c>
       <c r="F13" s="37">
-        <v>107699.74849422119</v>
+        <v>92261.0699352473</v>
       </c>
       <c r="G13" s="37">
-        <v>148018.83849998208</v>
+        <v>133166.27316072135</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="54">
-        <v>-0.19583333333333333</v>
-      </c>
-      <c r="D14" s="55">
-        <v>0.12182361918904425</v>
-      </c>
-      <c r="E14" s="55">
-        <v>0.27983747646538765</v>
-      </c>
-      <c r="F14" s="55">
-        <v>0.16516453995508912</v>
-      </c>
-      <c r="G14" s="55">
-        <v>0.12673281379661727</v>
+      <c r="C14" s="56">
+        <v>-0.2375</v>
+      </c>
+      <c r="D14" s="57">
+        <v>0.09398053046240151</v>
+      </c>
+      <c r="E14" s="57">
+        <v>0.26229703005504246</v>
+      </c>
+      <c r="F14" s="57">
+        <v>0.15626177170934255</v>
+      </c>
+      <c r="G14" s="57">
+        <v>0.12857511176333797</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="56">
+        <v>183</v>
+      </c>
+      <c r="C15" s="58">
         <v>7200</v>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="58">
         <v>7346.363636363636</v>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="58">
         <v>7526.3</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="58">
         <v>7732.422333333334</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="58">
         <v>7953.561670000001</v>
       </c>
-      <c r="H15" s="57" t="s">
-        <v>181</v>
+      <c r="H15" s="59" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C16" s="39">
-        <v>8610</v>
+        <v>8910</v>
       </c>
       <c r="D16" s="39">
-        <v>6451.40303030303</v>
+        <v>6655.948484848485</v>
       </c>
       <c r="E16" s="39">
-        <v>5420.159200878553</v>
+        <v>5552.1738626967335</v>
       </c>
       <c r="F16" s="39">
-        <v>6455.300355909877</v>
+        <v>6524.140319921778</v>
       </c>
       <c r="G16" s="39">
-        <v>6945.584419855979</v>
+        <v>6930.93158936315</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="31" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C17" s="33">
         <v>400</v>
@@ -2099,171 +2181,171 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="C18" s="58">
+        <v>187</v>
+      </c>
+      <c r="C18" s="60">
         <v>1720</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="60">
         <v>1206.9545454545453</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="60">
         <v>910.9325697674416</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F18" s="60">
         <v>781.265908431359</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G18" s="60">
         <v>723.6611744155073</v>
       </c>
-      <c r="H18" s="57" t="s">
-        <v>185</v>
+      <c r="H18" s="59" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="C19" s="59">
-        <v>-1410</v>
+        <v>189</v>
+      </c>
+      <c r="C19" s="61">
+        <v>-1710</v>
       </c>
       <c r="D19" s="45">
-        <v>894.960606060606</v>
+        <v>690.4151515151515</v>
       </c>
       <c r="E19" s="45">
-        <v>2106.140799121447</v>
+        <v>1974.126137303266</v>
       </c>
       <c r="F19" s="45">
-        <v>1277.1219774234569</v>
+        <v>1208.2820134115552</v>
       </c>
       <c r="G19" s="45">
-        <v>1007.9772501440224</v>
+        <v>1022.6300806368512</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="C20" s="54">
+        <v>190</v>
+      </c>
+      <c r="C20" s="56">
         <v>0.8666666666666667</v>
       </c>
-      <c r="D20" s="60">
+      <c r="D20" s="62">
         <v>0.5965103328795941</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="57">
         <v>0.439792195368242</v>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="57">
         <v>0.5087431894455497</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="57">
         <v>0.4584925214265674</v>
       </c>
-      <c r="H20" s="57" t="s">
-        <v>188</v>
+      <c r="H20" s="59" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="54">
+        <v>192</v>
+      </c>
+      <c r="C21" s="56">
         <v>0.2388888888888889</v>
       </c>
-      <c r="D21" s="60">
+      <c r="D21" s="62">
         <v>0.16429278554634325</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="57">
         <v>0.12103325269620419</v>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="57">
         <v>0.10103766643260505</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="57">
         <v>0.09098580037985765</v>
       </c>
-      <c r="H21" s="57" t="s">
-        <v>190</v>
+      <c r="H21" s="59" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="54">
-        <v>-0.19583333333333333</v>
-      </c>
-      <c r="D22" s="55">
-        <v>0.12182361918904425</v>
-      </c>
-      <c r="E22" s="55">
-        <v>0.2798374764653877</v>
-      </c>
-      <c r="F22" s="55">
-        <v>0.16516453995508906</v>
-      </c>
-      <c r="G22" s="55">
-        <v>0.12673281379661727</v>
-      </c>
-      <c r="H22" s="57" t="s">
-        <v>191</v>
+      <c r="C22" s="56">
+        <v>-0.2375</v>
+      </c>
+      <c r="D22" s="62">
+        <v>0.09398053046240151</v>
+      </c>
+      <c r="E22" s="57">
+        <v>0.2622970300550424</v>
+      </c>
+      <c r="F22" s="57">
+        <v>0.15626177170934255</v>
+      </c>
+      <c r="G22" s="57">
+        <v>0.12857511176333797</v>
+      </c>
+      <c r="H22" s="59" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="61">
+        <v>195</v>
+      </c>
+      <c r="C23" s="63">
         <v>2</v>
       </c>
-      <c r="D23" s="61">
+      <c r="D23" s="63">
         <v>2</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="63">
         <v>2</v>
       </c>
-      <c r="F23" s="61">
+      <c r="F23" s="63">
         <v>2</v>
       </c>
-      <c r="G23" s="61">
+      <c r="G23" s="63">
         <v>2</v>
       </c>
-      <c r="H23" s="57" t="s">
-        <v>193</v>
+      <c r="H23" s="59" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="E24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="F24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="G24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="H24" s="57" t="s">
-        <v>195</v>
+        <v>197</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="H24" s="59" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="63" t="str">
+        <v>199</v>
+      </c>
+      <c r="C25" s="65" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="63" t="str">
+      <c r="D25" s="65" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -2271,204 +2353,204 @@
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F25" s="63" t="str">
+      <c r="F25" s="65" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="63" t="str">
+      <c r="G25" s="65" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="59" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="64">
+        <v>200</v>
+      </c>
+      <c r="C26" s="66">
         <v>-2</v>
       </c>
-      <c r="D26" s="64">
-        <v>0</v>
-      </c>
-      <c r="E26" s="64">
+      <c r="D26" s="66">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="66">
+        <v>4</v>
+      </c>
+      <c r="F26" s="66">
         <v>5</v>
       </c>
-      <c r="F26" s="64">
+      <c r="G26" s="66">
         <v>6</v>
       </c>
-      <c r="G26" s="64">
-        <v>6</v>
-      </c>
-      <c r="H26" s="57" t="s">
-        <v>198</v>
+      <c r="H26" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="64">
-        <v>0</v>
-      </c>
-      <c r="D27" s="64">
-        <v>0</v>
-      </c>
-      <c r="E27" s="65">
-        <v>139</v>
-      </c>
-      <c r="F27" s="65">
-        <v>169</v>
-      </c>
-      <c r="G27" s="65">
-        <v>194</v>
-      </c>
-      <c r="H27" s="57" t="s">
-        <v>200</v>
+        <v>202</v>
+      </c>
+      <c r="C27" s="66">
+        <v>0</v>
+      </c>
+      <c r="D27" s="66">
+        <v>0</v>
+      </c>
+      <c r="E27" s="67">
+        <v>107</v>
+      </c>
+      <c r="F27" s="67">
+        <v>143</v>
+      </c>
+      <c r="G27" s="67">
+        <v>175</v>
+      </c>
+      <c r="H27" s="59" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="52" t="s">
-        <v>203</v>
-      </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52" t="s">
+      <c r="B29" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
+      <c r="C29" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="66" t="s">
-        <v>205</v>
-      </c>
-      <c r="C30" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="68" t="s">
-        <v>207</v>
-      </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69" t="s">
+      <c r="B30" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
+      <c r="C30" s="69" t="s">
+        <v>209</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>210</v>
+      </c>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="66" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="70" t="s">
-        <v>210</v>
-      </c>
-      <c r="D31" s="68" t="s">
-        <v>211</v>
-      </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69" t="s">
+      <c r="B31" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
+      <c r="C31" s="72" t="s">
+        <v>213</v>
+      </c>
+      <c r="D31" s="70" t="s">
+        <v>214</v>
+      </c>
+      <c r="E31" s="70"/>
+      <c r="F31" s="71" t="s">
+        <v>215</v>
+      </c>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="66" t="s">
-        <v>213</v>
+      <c r="B32" s="68" t="s">
+        <v>216</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="D32" s="68" t="s">
-        <v>215</v>
-      </c>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69" t="s">
-        <v>216</v>
-      </c>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
+        <v>217</v>
+      </c>
+      <c r="D32" s="70" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="70"/>
+      <c r="F32" s="71" t="s">
+        <v>219</v>
+      </c>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
+      <c r="B33" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="C33" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="D33" s="68" t="s">
-        <v>218</v>
-      </c>
-      <c r="E33" s="68"/>
-      <c r="F33" s="69" t="s">
-        <v>219</v>
-      </c>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
+      <c r="D33" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" s="70"/>
+      <c r="F33" s="71" t="s">
+        <v>222</v>
+      </c>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="66" t="s">
-        <v>220</v>
+      <c r="B34" s="68" t="s">
+        <v>223</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="D34" s="68" t="s">
-        <v>221</v>
-      </c>
-      <c r="E34" s="68"/>
-      <c r="F34" s="69" t="s">
-        <v>222</v>
-      </c>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
+        <v>217</v>
+      </c>
+      <c r="D34" s="70" t="s">
+        <v>224</v>
+      </c>
+      <c r="E34" s="70"/>
+      <c r="F34" s="71" t="s">
+        <v>225</v>
+      </c>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="66" t="s">
-        <v>223</v>
+      <c r="B35" s="68" t="s">
+        <v>226</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="D35" s="68" t="s">
-        <v>224</v>
-      </c>
-      <c r="E35" s="68"/>
-      <c r="F35" s="69" t="s">
-        <v>225</v>
-      </c>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
+        <v>217</v>
+      </c>
+      <c r="D35" s="70" t="s">
+        <v>227</v>
+      </c>
+      <c r="E35" s="70"/>
+      <c r="F35" s="71" t="s">
+        <v>228</v>
+      </c>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="66" t="s">
+      <c r="B37" s="68" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D37" s="34"/>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="71" t="s">
-        <v>227</v>
-      </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
+      <c r="B39" s="73" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3045,7 +3127,7 @@
         <v>87</v>
       </c>
       <c r="D52" s="21">
-        <v>3750</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
@@ -3053,7 +3135,7 @@
         <v>88</v>
       </c>
       <c r="D53" s="22">
-        <v>0.5136</v>
+        <v>0.23345454545454544</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -3686,23 +3768,23 @@
       </c>
       <c r="C21" s="33">
         <f>Assumptions!D52</f>
-        <v>3750</v>
+        <v>8250</v>
       </c>
       <c r="D21" s="33">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
-        <v>5676</v>
+        <v>10176</v>
       </c>
       <c r="E21" s="33">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
-        <v>8591.1936</v>
+        <v>12551.63345455</v>
       </c>
       <c r="F21" s="33">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
-        <v>13003.63063296</v>
+        <v>15481.86933739</v>
       </c>
       <c r="G21" s="33">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
-        <v>19682.29532605</v>
+        <v>19096.18210634</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -3711,23 +3793,23 @@
       </c>
       <c r="C22" s="35">
         <f>C18+C19+C20+C21</f>
-        <v>35550</v>
+        <v>40050</v>
       </c>
       <c r="D22" s="35">
         <f>D18+D19+D20+D21</f>
-        <v>45522.86666667</v>
+        <v>50022.86666667</v>
       </c>
       <c r="E22" s="35">
         <f>E18+E19+E20+E21</f>
-        <v>63304.53602636</v>
+        <v>67264.9758809</v>
       </c>
       <c r="F22" s="35">
         <f>F18+F19+F20+F21</f>
-        <v>90773.39361276</v>
+        <v>93251.63231718</v>
       </c>
       <c r="G22" s="35">
         <f>G18+G19+G20+G21</f>
-        <v>131957.43501824</v>
+        <v>131371.32179853</v>
       </c>
     </row>
   </sheetData>
@@ -3965,23 +4047,23 @@
       </c>
       <c r="C13" s="33">
         <f>Drivers!C22</f>
-        <v>35550</v>
+        <v>40050</v>
       </c>
       <c r="D13" s="33">
         <f>Drivers!D22</f>
-        <v>45522.86666667</v>
+        <v>50022.86666667</v>
       </c>
       <c r="E13" s="33">
         <f>Drivers!E22</f>
-        <v>63304.53602636</v>
+        <v>67264.9758809</v>
       </c>
       <c r="F13" s="33">
         <f>Drivers!F22</f>
-        <v>90773.39361276</v>
+        <v>93251.63231718</v>
       </c>
       <c r="G13" s="33">
         <f>Drivers!G22</f>
-        <v>131957.43501824</v>
+        <v>131371.32179853</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -3990,23 +4072,23 @@
       </c>
       <c r="C15" s="35">
         <f>C12+C13</f>
-        <v>129150</v>
+        <v>133650</v>
       </c>
       <c r="D15" s="35">
         <f>D12+D13</f>
-        <v>141930.86666667</v>
+        <v>146430.86666667</v>
       </c>
       <c r="E15" s="35">
         <f>E12+E13</f>
-        <v>162604.77602636</v>
+        <v>166565.2158809</v>
       </c>
       <c r="F15" s="35">
         <f>F12+F13</f>
-        <v>232390.81281276</v>
+        <v>234869.05151718</v>
       </c>
       <c r="G15" s="35">
         <f>G12+G13</f>
-        <v>277823.37679424</v>
+        <v>277237.26357453</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -4015,23 +4097,23 @@
       </c>
       <c r="C16" s="36">
         <f>C10-C15</f>
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D16" s="37">
         <f>D10-D15</f>
-        <v>19689.13333333</v>
+        <v>15189.13333333</v>
       </c>
       <c r="E16" s="37">
         <f>E10-E15</f>
-        <v>63184.22397364</v>
+        <v>59223.7841191</v>
       </c>
       <c r="F16" s="37">
         <f>F10-F15</f>
-        <v>45976.39118724</v>
+        <v>43498.15248282</v>
       </c>
       <c r="G16" s="37">
         <f>G10-G15</f>
-        <v>40319.09000576</v>
+        <v>40905.20322547</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -4040,23 +4122,23 @@
       </c>
       <c r="C17" s="38">
         <f>IF(C10&gt;0,C16/C10,0)</f>
-        <v>-0.19583333</v>
+        <v>-0.2375</v>
       </c>
       <c r="D17" s="38">
         <f>IF(D10&gt;0,D16/D10,0)</f>
-        <v>0.12182362</v>
+        <v>0.09398053</v>
       </c>
       <c r="E17" s="38">
         <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.27983748</v>
+        <v>0.26229703</v>
       </c>
       <c r="F17" s="38">
         <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>0.16516454</v>
+        <v>0.15626177</v>
       </c>
       <c r="G17" s="38">
         <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>0.12673281</v>
+        <v>0.12857511</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -4090,23 +4172,23 @@
       </c>
       <c r="C21" s="36">
         <f>C16-C19</f>
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D21" s="37">
         <f>D16-D19</f>
-        <v>19689.13333333</v>
+        <v>15189.13333333</v>
       </c>
       <c r="E21" s="37">
         <f>E16-E19</f>
-        <v>63184.22397364</v>
+        <v>59223.7841191</v>
       </c>
       <c r="F21" s="37">
         <f>F16-F19</f>
-        <v>45976.39118724</v>
+        <v>43498.15248282</v>
       </c>
       <c r="G21" s="37">
         <f>G16-G19</f>
-        <v>40319.09000576</v>
+        <v>40905.20322547</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -4115,23 +4197,23 @@
       </c>
       <c r="C22" s="38">
         <f>IF(C10&gt;0,C21/C10,0)</f>
-        <v>-0.19583333</v>
+        <v>-0.2375</v>
       </c>
       <c r="D22" s="38">
         <f>IF(D10&gt;0,D21/D10,0)</f>
-        <v>0.12182362</v>
+        <v>0.09398053</v>
       </c>
       <c r="E22" s="38">
         <f>IF(E10&gt;0,E21/E10,0)</f>
-        <v>0.27983748</v>
+        <v>0.26229703</v>
       </c>
       <c r="F22" s="38">
         <f>IF(F10&gt;0,F21/F10,0)</f>
-        <v>0.16516454</v>
+        <v>0.15626177</v>
       </c>
       <c r="G22" s="38">
         <f>IF(G10&gt;0,G21/G10,0)</f>
-        <v>0.12673281</v>
+        <v>0.12857511</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -4140,23 +4222,23 @@
       </c>
       <c r="C24" s="39">
         <f>C21</f>
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D24" s="39">
         <f>C24+D21</f>
-        <v>-1460.86666667</v>
+        <v>-10460.86666667</v>
       </c>
       <c r="E24" s="39">
         <f>D24+E21</f>
-        <v>61723.35730698</v>
+        <v>48762.91745243</v>
       </c>
       <c r="F24" s="39">
         <f>E24+F21</f>
-        <v>107699.74849422</v>
+        <v>92261.06993525</v>
       </c>
       <c r="G24" s="39">
         <f>F24+G21</f>
-        <v>148018.83849998</v>
+        <v>133166.27316072</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -4243,19 +4325,19 @@
       </c>
       <c r="D4" s="39">
         <f>C16</f>
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="E4" s="39">
         <f>D16</f>
-        <v>-1460.86666667</v>
+        <v>-10460.86666667</v>
       </c>
       <c r="F4" s="39">
         <f>E16</f>
-        <v>61723.35730698</v>
+        <v>48762.91745243</v>
       </c>
       <c r="G4" s="39">
         <f>F16</f>
-        <v>107699.74849422</v>
+        <v>92261.06993525</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -4264,23 +4346,23 @@
       </c>
       <c r="C5" s="33">
         <f>'5-Year P&amp;L'!C16</f>
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D5" s="33">
         <f>'5-Year P&amp;L'!D16</f>
-        <v>19689.13333333</v>
+        <v>15189.13333333</v>
       </c>
       <c r="E5" s="33">
         <f>'5-Year P&amp;L'!E16</f>
-        <v>63184.22397364</v>
+        <v>59223.7841191</v>
       </c>
       <c r="F5" s="33">
         <f>'5-Year P&amp;L'!F16</f>
-        <v>45976.39118724</v>
+        <v>43498.15248282</v>
       </c>
       <c r="G5" s="33">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>40319.09000576</v>
+        <v>40905.20322547</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -4389,23 +4471,23 @@
       </c>
       <c r="C13" s="33">
         <f>C5-C9</f>
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D13" s="33">
         <f>D5-D9</f>
-        <v>19689.13333333</v>
+        <v>15189.13333333</v>
       </c>
       <c r="E13" s="33">
         <f>E5-E9</f>
-        <v>63184.22397364</v>
+        <v>59223.7841191</v>
       </c>
       <c r="F13" s="33">
         <f>F5-F9</f>
-        <v>45976.39118724</v>
+        <v>43498.15248282</v>
       </c>
       <c r="G13" s="33">
         <f>G5-G9</f>
-        <v>40319.09000576</v>
+        <v>40905.20322547</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -4414,23 +4496,23 @@
       </c>
       <c r="C14" s="39">
         <f>C5-C9</f>
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D14" s="39">
         <f>D5-D9</f>
-        <v>19689.13333333</v>
+        <v>15189.13333333</v>
       </c>
       <c r="E14" s="39">
         <f>E5-E9</f>
-        <v>63184.22397364</v>
+        <v>59223.7841191</v>
       </c>
       <c r="F14" s="39">
         <f>F5-F9</f>
-        <v>45976.39118724</v>
+        <v>43498.15248282</v>
       </c>
       <c r="G14" s="39">
         <f>G5-G9</f>
-        <v>40319.09000576</v>
+        <v>40905.20322547</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -4439,23 +4521,23 @@
       </c>
       <c r="C16" s="36">
         <f>C4+C14</f>
-        <v>-21150</v>
+        <v>-25650</v>
       </c>
       <c r="D16" s="36">
         <f>D4+D14</f>
-        <v>-1460.86666667</v>
+        <v>-10460.86666667</v>
       </c>
       <c r="E16" s="37">
         <f>E4+E14</f>
-        <v>61723.35730698</v>
+        <v>48762.91745243</v>
       </c>
       <c r="F16" s="37">
         <f>F4+F14</f>
-        <v>107699.74849422</v>
+        <v>92261.06993525</v>
       </c>
       <c r="G16" s="37">
         <f>G4+G14</f>
-        <v>148018.83849998</v>
+        <v>133166.27316072</v>
       </c>
     </row>
   </sheetData>
@@ -4756,7 +4838,7 @@
       </c>
       <c r="C10" s="45">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>40319.09000576</v>
+        <v>40905.20322547</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
@@ -4771,7 +4853,7 @@
       </c>
       <c r="C13" s="47">
         <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
-        <v>0.12673281</v>
+        <v>0.12857511</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
@@ -4798,7 +4880,7 @@
       </c>
       <c r="C16" s="33">
         <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
-        <v>6946</v>
+        <v>6931</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -29,7 +29,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · llc_single</t>
+    <t>Generated May 1, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -29,7 +29,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · llc_single</t>
+    <t>Generated May 7, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1890,7 +1890,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1900,7 +1900,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>173</v>
       </c>
@@ -1910,8 +1910,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
@@ -1921,6 +1922,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
@@ -2411,7 +2413,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="54" t="s">
         <v>204</v>
       </c>
@@ -2427,8 +2429,9 @@
       </c>
       <c r="G29" s="54"/>
       <c r="H29" s="54"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="54"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="68" t="s">
         <v>208</v>
       </c>
@@ -2444,8 +2447,9 @@
       </c>
       <c r="G30" s="71"/>
       <c r="H30" s="71"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="71"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="68" t="s">
         <v>212</v>
       </c>
@@ -2461,8 +2465,9 @@
       </c>
       <c r="G31" s="71"/>
       <c r="H31" s="71"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="71"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="68" t="s">
         <v>216</v>
       </c>
@@ -2478,8 +2483,9 @@
       </c>
       <c r="G32" s="71"/>
       <c r="H32" s="71"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="71"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="68" t="s">
         <v>220</v>
       </c>
@@ -2495,8 +2501,9 @@
       </c>
       <c r="G33" s="71"/>
       <c r="H33" s="71"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="71"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="68" t="s">
         <v>223</v>
       </c>
@@ -2512,8 +2519,9 @@
       </c>
       <c r="G34" s="71"/>
       <c r="H34" s="71"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="71"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="68" t="s">
         <v>226</v>
       </c>
@@ -2529,6 +2537,7 @@
       </c>
       <c r="G35" s="71"/>
       <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="68" t="s">
@@ -2541,7 +2550,7 @@
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="73" t="s">
         <v>230</v>
       </c>
@@ -2551,27 +2560,28 @@
       <c r="F39" s="73"/>
       <c r="G39" s="73"/>
       <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B39:I39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2953,7 +2963,7 @@
         <v>65</v>
       </c>
       <c r="D26" s="22">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Homeschool_Co-Op_Mixed.xlsx
@@ -10,18 +10,20 @@
     <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Cash Flow &amp; DSCR" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
+    <sheet sheetId="7" name="AR &amp; Restricted Recon" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Staffing" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Loan Snapshot" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Summary" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Stress Tests" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Decision History" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Financial Health" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="265">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -29,7 +31,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · llc_single</t>
+    <t>Generated May 9, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +145,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -419,7 +421,10 @@
     <t>Operating Margin</t>
   </si>
   <si>
-    <t>Capital &amp; Debt Service</t>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Principal &amp; Capital Outlays</t>
   </si>
   <si>
     <t>Net Income</t>
@@ -467,6 +472,42 @@
     <t>Ending Cash</t>
   </si>
   <si>
+    <t>AR Schedule &amp; Restricted-vs-Unrestricted Cash Recon</t>
+  </si>
+  <si>
+    <t>AR = year's collected tuition × 30-day weighted delay ÷ 365. Bad debt = contracted − collected.</t>
+  </si>
+  <si>
+    <t>Accounts Receivable Schedule</t>
+  </si>
+  <si>
+    <t>Contracted Tuition (gross)</t>
+  </si>
+  <si>
+    <t>Collected Tuition (cash-basis)</t>
+  </si>
+  <si>
+    <t>Bad Debt (contracted − collected)</t>
+  </si>
+  <si>
+    <t>Year-end AR Balance (30-day delay)</t>
+  </si>
+  <si>
+    <t>Restricted vs Unrestricted Cash</t>
+  </si>
+  <si>
+    <t>Total Cash Position (accrual)</t>
+  </si>
+  <si>
+    <t>Restricted Cash (capital/program-restricted)</t>
+  </si>
+  <si>
+    <t>Unrestricted Cash (DSCR/runway basis)</t>
+  </si>
+  <si>
+    <t>Note: DSCR and cash-runway covenants in this packet are computed off Unrestricted Cash (row 14). Restricted gifts cannot legally service debt and are excluded from coverage tests.</t>
+  </si>
+  <si>
     <t>Staffing Detail</t>
   </si>
   <si>
@@ -533,6 +574,78 @@
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
+    <t>Standard Lender Stress Tests</t>
+  </si>
+  <si>
+    <t>Five fixed downside scenarios re-run on the canonical engine. Identical figures appear on the founder dashboard, consultant view, and lender packet PDF.</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Δ vs Base (Y1)</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Canonical engine output. All scenarios below are deltas vs this row.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Break-Even Students</t>
+  </si>
+  <si>
+    <t>Cash Runway (mo)</t>
+  </si>
+  <si>
+    <t>Break-Even Year</t>
+  </si>
+  <si>
+    <t>Enrollment -10%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 10% — the standard lender enrollment-miss sensitivity.</t>
+  </si>
+  <si>
+    <t>0y</t>
+  </si>
+  <si>
+    <t>Enrollment -20%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 20% — the stretch downside lenders use to confirm the school can survive a soft-launch.</t>
+  </si>
+  <si>
+    <t>ESA / Public Funding Delayed 3 Months</t>
+  </si>
+  <si>
+    <t>Year-1 ESA, school-choice, and public-funding receipts reduced by 25% (≈ 3 months delayed) to simulate a slow first disbursement.</t>
+  </si>
+  <si>
+    <t>Rent Shock +25%</t>
+  </si>
+  <si>
+    <t>Occupancy &amp; facility expense rows escalated by 25% — covers a lease renewal, market-rate reset, or unbudgeted CAM/utilities surprise.</t>
+  </si>
+  <si>
+    <t>Founder Comp Normalized to Market</t>
+  </si>
+  <si>
+    <t>Founder compensation re-cast at the market-rate benchmark (with benefits + payroll tax). The lender / board view of true operating cost.</t>
+  </si>
+  <si>
     <t>Decision History</t>
   </si>
   <si>
@@ -554,9 +667,6 @@
     <t>○ Red = action needed</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
     <t>Benchmark</t>
   </si>
   <si>
@@ -612,12 +722,6 @@
   </si>
   <si>
     <t>≥ 3 sources</t>
-  </si>
-  <si>
-    <t>DSCR</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Break-even Year</t>
@@ -726,7 +830,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -842,6 +946,18 @@
       <b/>
       <color rgb="FF16A34A"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -975,7 +1091,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1060,6 +1176,10 @@
     <xf numFmtId="167" fontId="19" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1073,15 +1193,40 @@
     <xf numFmtId="3" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1121,7 +1266,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1130,10 +1275,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1824,6 +1969,1345 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="31" t="str">
+        <f>Assumptions!D5</f>
+        <v>Liberty Learning Co-Op</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="31" t="str">
+        <f>Assumptions!D7</f>
+        <v>Homeschool Co-Op</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="31" t="str">
+        <f>Assumptions!D6</f>
+        <v>AZ</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="31">
+        <f>Assumptions!D8</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="32">
+        <f>Assumptions!D16</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="33">
+        <f>Drivers!G10</f>
+        <v>318142.4668</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="47">
+        <f>'5-Year P&amp;L'!G16</f>
+        <v>40905.20322547</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="29"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="49">
+        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
+        <v>0.12857511</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="38">
+        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
+        <v>0.45849252</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="33">
+        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
+        <v>7954</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="33">
+        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
+        <v>6931</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="42" t="str">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="43">
+        <f>'Cash Flow &amp; DSCR'!G11</f>
+        <v>99.9</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B21:C21"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFD97706"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="54" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="33">
+        <v>69608.75</v>
+      </c>
+      <c r="D7" s="33">
+        <v>177527.41499999998</v>
+      </c>
+      <c r="E7" s="33">
+        <v>290280.39995</v>
+      </c>
+      <c r="F7" s="33">
+        <v>381156.5375735</v>
+      </c>
+      <c r="G7" s="33">
+        <v>448957.53109133</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="D8" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G8" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="33">
+        <v>79608.75</v>
+      </c>
+      <c r="D9" s="33">
+        <v>257136.16499999998</v>
+      </c>
+      <c r="E9" s="33">
+        <v>547416.56495</v>
+      </c>
+      <c r="F9" s="33">
+        <v>928573.1025235001</v>
+      </c>
+      <c r="G9" s="33">
+        <v>1377530.6336148302</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="32">
+        <v>9</v>
+      </c>
+      <c r="D10" s="32">
+        <v>9</v>
+      </c>
+      <c r="E10" s="32">
+        <v>9</v>
+      </c>
+      <c r="F10" s="32">
+        <v>9</v>
+      </c>
+      <c r="G10" s="32">
+        <v>9</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="32">
+        <v>60</v>
+      </c>
+      <c r="D11" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="60" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="33">
+        <v>59150.41666666666</v>
+      </c>
+      <c r="D16" s="33">
+        <v>151679.91499999998</v>
+      </c>
+      <c r="E16" s="33">
+        <v>250356.1187</v>
+      </c>
+      <c r="F16" s="33">
+        <v>326336.4531985</v>
+      </c>
+      <c r="G16" s="33">
+        <v>392503.44460695505</v>
+      </c>
+      <c r="H16" s="39">
+        <v>-10458.333333333343</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="F17" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="33">
+        <v>69150.41666666666</v>
+      </c>
+      <c r="D18" s="33">
+        <v>220830.33166666664</v>
+      </c>
+      <c r="E18" s="33">
+        <v>471186.45036666666</v>
+      </c>
+      <c r="F18" s="33">
+        <v>797522.9035651666</v>
+      </c>
+      <c r="G18" s="33">
+        <v>1190026.3481721217</v>
+      </c>
+      <c r="H18" s="39">
+        <v>-10458.333333333343</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="32">
+        <v>9</v>
+      </c>
+      <c r="D19" s="32">
+        <v>9</v>
+      </c>
+      <c r="E19" s="32">
+        <v>9</v>
+      </c>
+      <c r="F19" s="32">
+        <v>9</v>
+      </c>
+      <c r="G19" s="32">
+        <v>9</v>
+      </c>
+      <c r="H19" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" s="32">
+        <v>60</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="33">
+        <v>38233.75</v>
+      </c>
+      <c r="D25" s="33">
+        <v>125832.415</v>
+      </c>
+      <c r="E25" s="33">
+        <v>210431.83745</v>
+      </c>
+      <c r="F25" s="33">
+        <v>285221.38991725</v>
+      </c>
+      <c r="G25" s="33">
+        <v>336049.35812258</v>
+      </c>
+      <c r="H25" s="39">
+        <v>-31375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E26" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="F26" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G26" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="33">
+        <v>48233.75</v>
+      </c>
+      <c r="D27" s="33">
+        <v>174066.16499999998</v>
+      </c>
+      <c r="E27" s="33">
+        <v>384498.00244999997</v>
+      </c>
+      <c r="F27" s="33">
+        <v>669719.39236725</v>
+      </c>
+      <c r="G27" s="33">
+        <v>1005768.75048983</v>
+      </c>
+      <c r="H27" s="39">
+        <v>-31375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="32">
+        <v>9</v>
+      </c>
+      <c r="D28" s="32">
+        <v>9</v>
+      </c>
+      <c r="E28" s="32">
+        <v>9</v>
+      </c>
+      <c r="F28" s="32">
+        <v>9</v>
+      </c>
+      <c r="G28" s="32">
+        <v>9</v>
+      </c>
+      <c r="H28" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="32">
+        <v>60</v>
+      </c>
+      <c r="D29" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="33">
+        <v>47733.75</v>
+      </c>
+      <c r="D34" s="33">
+        <v>177527.41499999998</v>
+      </c>
+      <c r="E34" s="33">
+        <v>290280.39995</v>
+      </c>
+      <c r="F34" s="33">
+        <v>381156.5375735</v>
+      </c>
+      <c r="G34" s="33">
+        <v>448957.53109133</v>
+      </c>
+      <c r="H34" s="39">
+        <v>-21875</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="D35" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="F35" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G35" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="H35" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="33">
+        <v>57733.75</v>
+      </c>
+      <c r="D36" s="33">
+        <v>235261.16499999998</v>
+      </c>
+      <c r="E36" s="33">
+        <v>525541.56495</v>
+      </c>
+      <c r="F36" s="33">
+        <v>906698.1025235001</v>
+      </c>
+      <c r="G36" s="33">
+        <v>1355655.6336148302</v>
+      </c>
+      <c r="H36" s="39">
+        <v>-21875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="32">
+        <v>10</v>
+      </c>
+      <c r="D37" s="32">
+        <v>9</v>
+      </c>
+      <c r="E37" s="32">
+        <v>9</v>
+      </c>
+      <c r="F37" s="32">
+        <v>9</v>
+      </c>
+      <c r="G37" s="32">
+        <v>9</v>
+      </c>
+      <c r="H37" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C38" s="32">
+        <v>60</v>
+      </c>
+      <c r="D38" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="33">
+        <v>64233.75</v>
+      </c>
+      <c r="D43" s="33">
+        <v>170889.16499999998</v>
+      </c>
+      <c r="E43" s="33">
+        <v>283448.3837</v>
+      </c>
+      <c r="F43" s="33">
+        <v>374125.07661725</v>
+      </c>
+      <c r="G43" s="33">
+        <v>441720.77998217376</v>
+      </c>
+      <c r="H43" s="39">
+        <v>-5375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="D44" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E44" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="F44" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G44" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="H44" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="33">
+        <v>74233.75</v>
+      </c>
+      <c r="D45" s="33">
+        <v>245122.91499999998</v>
+      </c>
+      <c r="E45" s="33">
+        <v>528571.2986999999</v>
+      </c>
+      <c r="F45" s="33">
+        <v>902696.3753172499</v>
+      </c>
+      <c r="G45" s="33">
+        <v>1344417.1552994237</v>
+      </c>
+      <c r="H45" s="39">
+        <v>-5375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" s="32">
+        <v>9</v>
+      </c>
+      <c r="D46" s="32">
+        <v>9</v>
+      </c>
+      <c r="E46" s="32">
+        <v>9</v>
+      </c>
+      <c r="F46" s="32">
+        <v>9</v>
+      </c>
+      <c r="G46" s="32">
+        <v>9</v>
+      </c>
+      <c r="H46" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47" s="32">
+        <v>60</v>
+      </c>
+      <c r="D47" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" s="55"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="55"/>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C52" s="33">
+        <v>67055.75</v>
+      </c>
+      <c r="D52" s="33">
+        <v>174259.57499999998</v>
+      </c>
+      <c r="E52" s="33">
+        <v>287629.10945</v>
+      </c>
+      <c r="F52" s="33">
+        <v>377902.73907350004</v>
+      </c>
+      <c r="G52" s="33">
+        <v>446435.16709133</v>
+      </c>
+      <c r="H52" s="39">
+        <v>-2553</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C53" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="D53" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E53" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="F53" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G53" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="H53" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" s="33">
+        <v>79608.75</v>
+      </c>
+      <c r="D54" s="33">
+        <v>257136.16499999998</v>
+      </c>
+      <c r="E54" s="33">
+        <v>547416.56495</v>
+      </c>
+      <c r="F54" s="33">
+        <v>928573.1025235001</v>
+      </c>
+      <c r="G54" s="33">
+        <v>1377530.6336148302</v>
+      </c>
+      <c r="H54" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" s="32">
+        <v>9</v>
+      </c>
+      <c r="D55" s="32">
+        <v>9</v>
+      </c>
+      <c r="E55" s="32">
+        <v>9</v>
+      </c>
+      <c r="F55" s="32">
+        <v>9</v>
+      </c>
+      <c r="G55" s="32">
+        <v>9</v>
+      </c>
+      <c r="H55" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C56" s="32">
+        <v>60</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1839,7 +3323,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -1849,26 +3333,26 @@
       <c r="H1" s="13"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="B2" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
+      <c r="B4" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1884,7 +3368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -1902,7 +3386,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1925,37 +3409,37 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>176</v>
+      <c r="B4" s="62" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="54" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="55" t="s">
+      <c r="B6" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="H6" s="55" t="s">
-        <v>178</v>
+      <c r="H6" s="66" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1980,7 +3464,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="C8" s="33">
         <v>108000</v>
@@ -2000,7 +3484,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="C9" s="33">
         <v>93600</v>
@@ -2020,7 +3504,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="C10" s="33">
         <v>40050</v>
@@ -2040,7 +3524,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="C11" s="33">
         <v>0</v>
@@ -2060,7 +3544,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C12" s="36">
         <v>-25650</v>
@@ -2080,7 +3564,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C13" s="36">
         <v>-25650</v>
@@ -2100,50 +3584,50 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="56">
+        <v>135</v>
+      </c>
+      <c r="C14" s="67">
         <v>-0.2375</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="68">
         <v>0.09398053046240151</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="68">
         <v>0.26229703005504246</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="68">
         <v>0.15626177170934255</v>
       </c>
-      <c r="G14" s="57">
+      <c r="G14" s="68">
         <v>0.12857511176333797</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="C15" s="58">
+        <v>219</v>
+      </c>
+      <c r="C15" s="69">
         <v>7200</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D15" s="69">
         <v>7346.363636363636</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E15" s="69">
         <v>7526.3</v>
       </c>
-      <c r="F15" s="58">
+      <c r="F15" s="69">
         <v>7732.422333333334</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G15" s="69">
         <v>7953.561670000001</v>
       </c>
-      <c r="H15" s="59" t="s">
-        <v>184</v>
+      <c r="H15" s="70" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="C16" s="39">
         <v>8910</v>
@@ -2163,7 +3647,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="31" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="C17" s="33">
         <v>400</v>
@@ -2183,171 +3667,171 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" s="60">
+        <v>223</v>
+      </c>
+      <c r="C18" s="71">
         <v>1720</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="71">
         <v>1206.9545454545453</v>
       </c>
-      <c r="E18" s="60">
+      <c r="E18" s="71">
         <v>910.9325697674416</v>
       </c>
-      <c r="F18" s="60">
+      <c r="F18" s="71">
         <v>781.265908431359</v>
       </c>
-      <c r="G18" s="60">
+      <c r="G18" s="71">
         <v>723.6611744155073</v>
       </c>
-      <c r="H18" s="59" t="s">
-        <v>188</v>
+      <c r="H18" s="70" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="C19" s="61">
+        <v>225</v>
+      </c>
+      <c r="C19" s="72">
         <v>-1710</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="47">
         <v>690.4151515151515</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="47">
         <v>1974.126137303266</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="47">
         <v>1208.2820134115552</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="47">
         <v>1022.6300806368512</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="C20" s="56">
+        <v>226</v>
+      </c>
+      <c r="C20" s="67">
         <v>0.8666666666666667</v>
       </c>
-      <c r="D20" s="62">
+      <c r="D20" s="73">
         <v>0.5965103328795941</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="68">
         <v>0.439792195368242</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F20" s="68">
         <v>0.5087431894455497</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G20" s="68">
         <v>0.4584925214265674</v>
       </c>
-      <c r="H20" s="59" t="s">
-        <v>191</v>
+      <c r="H20" s="70" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="C21" s="56">
+        <v>228</v>
+      </c>
+      <c r="C21" s="67">
         <v>0.2388888888888889</v>
       </c>
-      <c r="D21" s="62">
+      <c r="D21" s="73">
         <v>0.16429278554634325</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="68">
         <v>0.12103325269620419</v>
       </c>
-      <c r="F21" s="57">
+      <c r="F21" s="68">
         <v>0.10103766643260505</v>
       </c>
-      <c r="G21" s="57">
+      <c r="G21" s="68">
         <v>0.09098580037985765</v>
       </c>
-      <c r="H21" s="59" t="s">
-        <v>193</v>
+      <c r="H21" s="70" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="67">
         <v>-0.2375</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="73">
         <v>0.09398053046240151</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E22" s="68">
         <v>0.2622970300550424</v>
       </c>
-      <c r="F22" s="57">
+      <c r="F22" s="68">
         <v>0.15626177170934255</v>
       </c>
-      <c r="G22" s="57">
+      <c r="G22" s="68">
         <v>0.12857511176333797</v>
       </c>
-      <c r="H22" s="59" t="s">
-        <v>194</v>
+      <c r="H22" s="70" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="C23" s="63">
+        <v>231</v>
+      </c>
+      <c r="C23" s="74">
         <v>2</v>
       </c>
-      <c r="D23" s="63">
+      <c r="D23" s="74">
         <v>2</v>
       </c>
-      <c r="E23" s="63">
+      <c r="E23" s="74">
         <v>2</v>
       </c>
-      <c r="F23" s="63">
+      <c r="F23" s="74">
         <v>2</v>
       </c>
-      <c r="G23" s="63">
+      <c r="G23" s="74">
         <v>2</v>
       </c>
-      <c r="H23" s="59" t="s">
-        <v>196</v>
+      <c r="H23" s="70" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="C24" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="E24" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="G24" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="H24" s="59" t="s">
-        <v>198</v>
+        <v>191</v>
+      </c>
+      <c r="C24" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="F24" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="G24" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="H24" s="70" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="C25" s="65" t="str">
+        <v>233</v>
+      </c>
+      <c r="C25" s="76" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="65" t="str">
+      <c r="D25" s="76" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -2355,212 +3839,212 @@
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F25" s="65" t="str">
+      <c r="F25" s="76" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="65" t="str">
+      <c r="G25" s="76" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="59" t="s">
+      <c r="H25" s="70" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="C26" s="66">
+        <v>234</v>
+      </c>
+      <c r="C26" s="77">
         <v>-2</v>
       </c>
-      <c r="D26" s="66">
+      <c r="D26" s="77">
         <v>-1</v>
       </c>
-      <c r="E26" s="66">
+      <c r="E26" s="77">
         <v>4</v>
       </c>
-      <c r="F26" s="66">
+      <c r="F26" s="77">
         <v>5</v>
       </c>
-      <c r="G26" s="66">
+      <c r="G26" s="77">
         <v>6</v>
       </c>
-      <c r="H26" s="59" t="s">
-        <v>201</v>
+      <c r="H26" s="70" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="C27" s="66">
-        <v>0</v>
-      </c>
-      <c r="D27" s="66">
-        <v>0</v>
-      </c>
-      <c r="E27" s="67">
+        <v>236</v>
+      </c>
+      <c r="C27" s="77">
+        <v>0</v>
+      </c>
+      <c r="D27" s="77">
+        <v>0</v>
+      </c>
+      <c r="E27" s="78">
         <v>107</v>
       </c>
-      <c r="F27" s="67">
+      <c r="F27" s="78">
         <v>143</v>
       </c>
-      <c r="G27" s="67">
+      <c r="G27" s="78">
         <v>175</v>
       </c>
-      <c r="H27" s="59" t="s">
-        <v>203</v>
+      <c r="H27" s="70" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="54" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>205</v>
-      </c>
-      <c r="D29" s="54" t="s">
-        <v>206</v>
-      </c>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54" t="s">
-        <v>207</v>
-      </c>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
+      <c r="B29" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="69" t="s">
-        <v>209</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>210</v>
-      </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71" t="s">
-        <v>211</v>
-      </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
+      <c r="B30" s="79" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="D30" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82" t="s">
+        <v>245</v>
+      </c>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="68" t="s">
-        <v>212</v>
-      </c>
-      <c r="C31" s="72" t="s">
-        <v>213</v>
-      </c>
-      <c r="D31" s="70" t="s">
-        <v>214</v>
-      </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71" t="s">
-        <v>215</v>
-      </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
+      <c r="B31" s="79" t="s">
+        <v>246</v>
+      </c>
+      <c r="C31" s="83" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="E31" s="81"/>
+      <c r="F31" s="82" t="s">
+        <v>249</v>
+      </c>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="68" t="s">
-        <v>216</v>
+      <c r="B32" s="79" t="s">
+        <v>250</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="D32" s="70" t="s">
-        <v>218</v>
-      </c>
-      <c r="E32" s="70"/>
-      <c r="F32" s="71" t="s">
-        <v>219</v>
-      </c>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
+        <v>251</v>
+      </c>
+      <c r="D32" s="81" t="s">
+        <v>252</v>
+      </c>
+      <c r="E32" s="81"/>
+      <c r="F32" s="82" t="s">
+        <v>253</v>
+      </c>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="68" t="s">
-        <v>220</v>
+      <c r="B33" s="79" t="s">
+        <v>254</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="D33" s="70" t="s">
-        <v>221</v>
-      </c>
-      <c r="E33" s="70"/>
-      <c r="F33" s="71" t="s">
-        <v>222</v>
-      </c>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
+        <v>251</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="E33" s="81"/>
+      <c r="F33" s="82" t="s">
+        <v>256</v>
+      </c>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="68" t="s">
-        <v>223</v>
+      <c r="B34" s="79" t="s">
+        <v>257</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="D34" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="E34" s="70"/>
-      <c r="F34" s="71" t="s">
-        <v>225</v>
-      </c>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
+        <v>251</v>
+      </c>
+      <c r="D34" s="81" t="s">
+        <v>258</v>
+      </c>
+      <c r="E34" s="81"/>
+      <c r="F34" s="82" t="s">
+        <v>259</v>
+      </c>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="68" t="s">
-        <v>226</v>
+      <c r="B35" s="79" t="s">
+        <v>260</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="D35" s="70" t="s">
-        <v>227</v>
-      </c>
-      <c r="E35" s="70"/>
-      <c r="F35" s="71" t="s">
-        <v>228</v>
-      </c>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
+        <v>251</v>
+      </c>
+      <c r="D35" s="81" t="s">
+        <v>261</v>
+      </c>
+      <c r="E35" s="81"/>
+      <c r="F35" s="82" t="s">
+        <v>262</v>
+      </c>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+      <c r="I35" s="82"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="68" t="s">
+      <c r="B37" s="79" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="D37" s="34"/>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="73" t="s">
-        <v>230</v>
-      </c>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
+      <c r="B39" s="84" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" s="84"/>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3840,7 +5324,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G25"/>
+  <dimension ref="B1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4155,119 +5639,139 @@
       <c r="B19" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="33" t="str">
-        <f>'Cash Flow &amp; DSCR'!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="33" t="str">
-        <f>'Cash Flow &amp; DSCR'!D9</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="33" t="str">
-        <f>'Cash Flow &amp; DSCR'!E9</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="33" t="str">
-        <f>'Cash Flow &amp; DSCR'!F9</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="33" t="str">
-        <f>'Cash Flow &amp; DSCR'!G9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="34" t="s">
+      <c r="C19" s="33">
+        <v>0</v>
+      </c>
+      <c r="D19" s="33">
+        <v>0</v>
+      </c>
+      <c r="E19" s="33">
+        <v>0</v>
+      </c>
+      <c r="F19" s="33">
+        <v>0</v>
+      </c>
+      <c r="G19" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="36">
-        <f>C16-C19</f>
+      <c r="C20" s="33" t="str">
+        <f>'Cash Flow &amp; DSCR'!C9-C19</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="33" t="str">
+        <f>'Cash Flow &amp; DSCR'!D9-D19</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="33" t="str">
+        <f>'Cash Flow &amp; DSCR'!E9-E19</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="33" t="str">
+        <f>'Cash Flow &amp; DSCR'!F9-F19</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="33" t="str">
+        <f>'Cash Flow &amp; DSCR'!G9-G19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="36">
+        <f>C16-C19-C20</f>
         <v>-25650</v>
       </c>
-      <c r="D21" s="37">
-        <f>D16-D19</f>
+      <c r="D22" s="37">
+        <f>D16-D19-D20</f>
         <v>15189.13333333</v>
       </c>
-      <c r="E21" s="37">
-        <f>E16-E19</f>
+      <c r="E22" s="37">
+        <f>E16-E19-E20</f>
         <v>59223.7841191</v>
       </c>
-      <c r="F21" s="37">
-        <f>F16-F19</f>
+      <c r="F22" s="37">
+        <f>F16-F19-F20</f>
         <v>43498.15248282</v>
       </c>
-      <c r="G21" s="37">
-        <f>G16-G19</f>
+      <c r="G22" s="37">
+        <f>G16-G19-G20</f>
         <v>40905.20322547</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="38">
-        <f>IF(C10&gt;0,C21/C10,0)</f>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="38">
+        <f>IF(C10&gt;0,C22/C10,0)</f>
         <v>-0.2375</v>
       </c>
-      <c r="D22" s="38">
-        <f>IF(D10&gt;0,D21/D10,0)</f>
+      <c r="D23" s="38">
+        <f>IF(D10&gt;0,D22/D10,0)</f>
         <v>0.09398053</v>
       </c>
-      <c r="E22" s="38">
-        <f>IF(E10&gt;0,E21/E10,0)</f>
+      <c r="E23" s="38">
+        <f>IF(E10&gt;0,E22/E10,0)</f>
         <v>0.26229703</v>
       </c>
-      <c r="F22" s="38">
-        <f>IF(F10&gt;0,F21/F10,0)</f>
+      <c r="F23" s="38">
+        <f>IF(F10&gt;0,F22/F10,0)</f>
         <v>0.15626177</v>
       </c>
-      <c r="G22" s="38">
-        <f>IF(G10&gt;0,G21/G10,0)</f>
+      <c r="G23" s="38">
+        <f>IF(G10&gt;0,G22/G10,0)</f>
         <v>0.12857511</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="39">
-        <f>C21</f>
-        <v>-25650</v>
-      </c>
-      <c r="D24" s="39">
-        <f>C24+D21</f>
-        <v>-10460.86666667</v>
-      </c>
-      <c r="E24" s="39">
-        <f>D24+E21</f>
-        <v>48762.91745243</v>
-      </c>
-      <c r="F24" s="39">
-        <f>E24+F21</f>
-        <v>92261.06993525</v>
-      </c>
-      <c r="G24" s="39">
-        <f>F24+G21</f>
-        <v>133166.27316072</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="41" t="s">
+      <c r="C25" s="39">
+        <f>C22</f>
+        <v>-25650</v>
+      </c>
+      <c r="D25" s="39">
+        <f>C25+D22</f>
+        <v>-10460.86666667</v>
+      </c>
+      <c r="E25" s="39">
+        <f>D25+E22</f>
+        <v>48762.91745243</v>
+      </c>
+      <c r="F25" s="39">
+        <f>E25+F22</f>
+        <v>92261.06993525</v>
+      </c>
+      <c r="G25" s="39">
+        <f>F25+G22</f>
+        <v>133166.27316072</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="F25" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="40" t="s">
+      <c r="C26" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="40" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4299,7 +5803,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4327,7 +5831,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C4" s="39" t="str">
         <f>Assumptions!D57</f>
@@ -4352,7 +5856,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C5" s="33">
         <f>'5-Year P&amp;L'!C16</f>
@@ -4377,7 +5881,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="33" t="str">
         <f>Assumptions!D58</f>
@@ -4402,7 +5906,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C8" s="33" t="str">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4427,7 +5931,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C9" s="35" t="str">
         <f>C7+C8</f>
@@ -4452,7 +5956,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="42" t="str">
         <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
@@ -4477,7 +5981,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C13" s="33">
         <f>C5-C9</f>
@@ -4502,7 +6006,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="39">
         <f>C5-C9</f>
@@ -4527,7 +6031,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C16" s="36">
         <f>C4+C14</f>
@@ -4565,6 +6069,267 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF7C3AED"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:G17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="29"/>
+      <c r="C4" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="33">
+        <v>0</v>
+      </c>
+      <c r="D6" s="33">
+        <v>0</v>
+      </c>
+      <c r="E6" s="33">
+        <v>0</v>
+      </c>
+      <c r="F6" s="33">
+        <v>0</v>
+      </c>
+      <c r="G6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="33">
+        <v>0</v>
+      </c>
+      <c r="D7" s="33">
+        <v>0</v>
+      </c>
+      <c r="E7" s="33">
+        <v>0</v>
+      </c>
+      <c r="F7" s="33">
+        <v>0</v>
+      </c>
+      <c r="G7" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="37" t="str">
+        <f>C6-C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="37" t="str">
+        <f>D6-D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="37" t="str">
+        <f>E6-E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="37" t="str">
+        <f>F6-F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="37" t="str">
+        <f>G6-G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="35" t="str">
+        <f>C7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="35" t="str">
+        <f>D7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="35" t="str">
+        <f>E7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="35" t="str">
+        <f>F7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="35" t="str">
+        <f>G7*30/365</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="33">
+        <v>-25650</v>
+      </c>
+      <c r="D12" s="33">
+        <v>-10460.866666666669</v>
+      </c>
+      <c r="E12" s="33">
+        <v>48762.91745243131</v>
+      </c>
+      <c r="F12" s="33">
+        <v>92261.0699352473</v>
+      </c>
+      <c r="G12" s="33">
+        <v>133166.27316072135</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="33">
+        <v>0</v>
+      </c>
+      <c r="D13" s="33">
+        <v>0</v>
+      </c>
+      <c r="E13" s="33">
+        <v>0</v>
+      </c>
+      <c r="F13" s="33">
+        <v>0</v>
+      </c>
+      <c r="G13" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="36">
+        <f>C12-C13</f>
+        <v>-25650</v>
+      </c>
+      <c r="D14" s="36">
+        <f>D12-D13</f>
+        <v>-10460.86666667</v>
+      </c>
+      <c r="E14" s="37">
+        <f>E12-E13</f>
+        <v>48762.91745243</v>
+      </c>
+      <c r="F14" s="37">
+        <f>F12-F13</f>
+        <v>92261.06993525</v>
+      </c>
+      <c r="G14" s="37">
+        <f>G12-G13</f>
+        <v>133166.27316072</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B16:G17"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4578,7 +6343,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4606,7 +6371,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="31" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="C4" s="32">
         <f>Drivers!C12</f>
@@ -4631,7 +6396,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C5" s="32">
         <f>Assumptions!D35</f>
@@ -4656,25 +6421,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="44">
+        <v>164</v>
+      </c>
+      <c r="C6" s="46">
         <f>C4+C5</f>
         <v>2</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="46">
         <f>D4+D5</f>
         <v>2</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="46">
         <f>E4+E5</f>
         <v>2</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="46">
         <f>F4+F5</f>
         <v>3</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="46">
         <f>G4+G5</f>
         <v>3</v>
       </c>
@@ -4691,7 +6456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
@@ -4707,13 +6472,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="31" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C3" s="33" t="str">
         <f>Assumptions!D59</f>
@@ -4722,7 +6487,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="31" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C4" s="38">
         <f>Assumptions!D60</f>
@@ -4740,7 +6505,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C6" s="39" t="str">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4749,7 +6514,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C8" s="42" t="str">
         <f>'Cash Flow &amp; DSCR'!C11</f>
@@ -4766,174 +6531,4 @@
     <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="31" t="str">
-        <f>Assumptions!D5</f>
-        <v>Liberty Learning Co-Op</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="31" t="str">
-        <f>Assumptions!D7</f>
-        <v>Homeschool Co-Op</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="31" t="str">
-        <f>Assumptions!D6</f>
-        <v>AZ</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="31">
-        <f>Assumptions!D8</f>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="32">
-        <f>Assumptions!D16</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="33">
-        <f>Drivers!G10</f>
-        <v>318142.4668</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="45">
-        <f>'5-Year P&amp;L'!G16</f>
-        <v>40905.20322547</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="29"/>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="C13" s="47">
-        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
-        <v>0.12857511</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" s="38">
-        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
-        <v>0.45849252</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="C15" s="33">
-        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
-        <v>7954</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="C16" s="33">
-        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
-        <v>6931</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="C17" s="42" t="str">
-        <f>'Cash Flow &amp; DSCR'!C11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="C18" s="43">
-        <f>'Cash Flow &amp; DSCR'!G11</f>
-        <v>99.9</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="C19" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C21" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>